--- a/docs/design/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者明細検索画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者明細検索画面_v1.0.xlsx
@@ -1539,7 +1539,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -1555,7 +1555,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -2078,7 +2078,7 @@
       <c r="F4" s="11" t="n"/>
       <c r="G4" s="20" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="H4" s="10" t="n"/>
@@ -2851,7 +2851,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -2867,7 +2867,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -6484,7 +6484,7 @@
       <c r="E2" s="11" t="n"/>
       <c r="F2" s="20" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="G2" s="10" t="n"/>
@@ -9101,7 +9101,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">展開された詳細検索エリアの項目を確認（引落元口座支店コード、引落元口座支店名、連絡先１、メールアドレス、請求開始月、適用日、支払方法）
+            <t xml:space="preserve">展開された詳細検索エリアの項目を確認（引落元口座支店、連絡先、メールアドレス、請求開始月、適用日、支払方法、郵送区分、新聞単価、備考）
 </t>
           </r>
           <r>
@@ -9178,7 +9178,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">引落元口座支店コード、引落元口座支店名、連絡先１、メールアドレス、請求開始月、適用日（開始・終了の2入力欄）、支払方法（ラジオ7択：口座引落・現金集金・振込集金・JA施設等・給与天引き・クレジットカード・その他）が表示されること
+            <t xml:space="preserve">引落元口座支店、連絡先、メールアドレス、請求開始月（開始・終了の2入力欄・YYYYMM月選択）、適用日（開始・終了の2入力欄）、支払方法（ラジオ7択：口座引落・現金集金・振込集金・JA施設等・給与天引き・クレジットカード・その他）、郵送区分（プルダウン：0:空 / 1:郵送）、新聞単価（プルダウン）、備考（テキスト・部分一致）が表示されること
 </t>
           </r>
           <r>
@@ -11213,7 +11213,7 @@
       <c r="D31" s="11" t="n"/>
       <c r="E31" s="46" t="inlineStr">
         <is>
-          <t>詳細検索項目 最大長境界（引落元口座支店コード3文字、請求開始月6文字、連絡先１ 15文字）</t>
+          <t>詳細検索項目 最大長境界（引落元口座支店100文字、請求開始月（開始）YYYYMM 6桁、連絡先 15文字）</t>
         </is>
       </c>
       <c r="F31" s="10" t="n"/>
@@ -11247,7 +11247,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">引落元口座支店コードに 3 文字を入力し、「検索」を押下、続けて 4 文字を入力し、「検索」を押下
+            <t xml:space="preserve">引落元口座支店に 100 文字を入力し、「検索」を押下、続けて 101 文字を入力し、「検索」を押下
 </t>
           </r>
           <r>
@@ -11264,7 +11264,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">請求開始月に 6 文字を入力し、「検索」を押下、続けて 7 文字を入力し、「検索」を押下
+            <t xml:space="preserve">請求開始月（開始）に 6 桁（YYYYMM）を入力し、「検索」を押下、続けて 7 桁を入力し、「検索」を押下
 </t>
           </r>
           <r>
@@ -11281,7 +11281,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>連絡先１に 15 文字を入力し、「検索」を押下、続けて 16 文字を入力し、「検索」を押下</t>
+            <t>連絡先に 15 文字を入力し、「検索」を押下、続けて 16 文字を入力し、「検索」を押下</t>
           </r>
         </is>
       </c>
@@ -11307,7 +11307,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">3 文字は HTTPステータスコード200で正常に検索されること、4 文字は桁数超過エラーが表示されること（`error_code: VALIDATION_ERROR`、`errors[]` に `field: jastem_toriatsukai_tenpo_code`）
+            <t xml:space="preserve">100 文字は HTTPステータスコード200で正常に検索されること、101 文字は桁数超過エラーが表示されること（`error_code: VALIDATION_ERROR`、`errors[]` に `field: bank_branch`）
 </t>
           </r>
           <r>
@@ -11324,7 +11324,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">6 文字は HTTPステータスコード200で正常に検索されること、7 文字は桁数超過エラーが表示されること（`errors[]` に `field: seikyu_kaishi_month`）
+            <t xml:space="preserve">6 桁（YYYYMM）は HTTPステータスコード200で正常に検索されること、7 桁は形式エラー（`請求開始月はYYYYMMの形式で指定してください。`）が表示されること（`errors[]` に `field: seikyu_kaishi_month_from`）
 </t>
           </r>
           <r>
@@ -11341,7 +11341,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">15 文字は HTTPステータスコード200で正常に検索されること、16 文字は桁数超過エラーが表示されること（`errors[]` に `field: renrakusaki_1`）
+            <t xml:space="preserve">15 文字は HTTPステータスコード200で正常に検索されること、16 文字は桁数超過エラーが表示されること（`errors[]` に `field: renrakusaki`）
 </t>
           </r>
           <r>
@@ -11358,15 +11358,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・引落元口座支店コードは物理カラム `bank_branch_code`（最大3文字）に対する部分一致
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・引落元口座支店名は物理カラム `bank_branch_name`（最大100文字）に対する部分一致
+            <t xml:space="preserve">・引落元口座支店は物理カラム `bank_branch_code` / `bank_branch_name`（最大100文字）に対する OR 部分一致
 </t>
           </r>
           <r>
@@ -13775,7 +13767,7 @@
       <c r="BP41" s="10" t="n"/>
       <c r="BQ41" s="11" t="n"/>
     </row>
-    <row r="42" ht="352" customHeight="1">
+    <row r="42" ht="368" customHeight="1">
       <c r="A42" s="44" t="n">
         <v>27</v>
       </c>
@@ -13900,7 +13892,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">検索結果なしのメッセージ `該当するデータが存在しません。` が一覧テーブル外に表示されること
+            <t xml:space="preserve">検索結果なしのメッセージ `検索結果が見つかりませんでした。` が一覧テーブル外に表示されること
 </t>
           </r>
           <r>
@@ -13934,7 +13926,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・ACSMS-MSG-014-002 該当
+            <t xml:space="preserve">・ACSMS-MSG-014-002 検索結果が見つかりませんでした。
 </t>
           </r>
           <r>
@@ -14707,7 +14699,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード200が返却されること（レスポンス `{ "message": "購読者を削除しました。" }`、トースト `購読者を削除しました。` 表示）
+            <t xml:space="preserve">HTTPステータスコード200が返却されること（レスポンス `{ "message": "削除しました。" }`、トースト `削除しました。` 表示）
 </t>
           </r>
           <r>
@@ -15789,7 +15781,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">ファイル名が `dokusya_export_YYYYMMDD_HHmmss.xlsx`（JST）であること、`Content-Type` が `application/vnd.openxmlformats-officedocument.spreadsheetml.sheet` であること、ヘッダー行が `管理支店, 支店, 組合員コード, 購読者名, 連絡先１, 連絡先２, 配達先郵便, 配達先住所, 販売店コード, 販売店名, 購読開始日, 購読中止日`（12列）であること
+            <t xml:space="preserve">ファイル名が `購読者一覧出力_YYYYMMDD_HHmmss.xlsx`（JST）であること、`Content-Type` が `application/vnd.openxmlformats-officedocument.spreadsheetml.sheet` であること、ヘッダー行が `管理支店, 支店, 組合員コード, 購読者名, 連絡先１, 連絡先２, 配達先郵便, 配達先住所, 販売店コード, 販売店名, 購読開始日, 購読中止日`（12列）であること
 </t>
           </r>
           <r>

--- a/docs/design/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者明細検索画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者明細検索画面_v1.0.xlsx
@@ -1539,7 +1539,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -1555,7 +1555,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -2078,7 +2078,7 @@
       <c r="F4" s="11" t="n"/>
       <c r="G4" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="H4" s="10" t="n"/>
@@ -2851,7 +2851,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -2867,7 +2867,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -6346,7 +6346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ59"/>
+  <dimension ref="A1:BQ64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6484,7 +6484,7 @@
       <c r="E2" s="11" t="n"/>
       <c r="F2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="G2" s="10" t="n"/>
@@ -18065,10 +18065,1422 @@
       <c r="BP59" s="10" t="n"/>
       <c r="BQ59" s="11" t="n"/>
     </row>
+    <row r="60" ht="450" customHeight="1">
+      <c r="A60" s="44" t="n">
+        <v>44</v>
+      </c>
+      <c r="B60" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-014-044</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="46" t="inlineStr">
+        <is>
+          <t>購読中止 — 電子版：予約中の終了月がポップアップに復元される</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="11" t="n"/>
+      <c r="J60" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・事前データ：電子版購読者（`dokusya_id=1020, dokusya_shubetsu=2, shiharai_hoho≠6, seikyu_kaishi_month='202604'`）に 2030/07 の解約予約が登録済（到来日バッチ未実行＝`kaiyaku_flg=false`）</t>
+        </is>
+      </c>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="11" t="n"/>
+      <c r="Q60" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読者明細検索画面で該当行の「購読中止」リンクをクリックする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ポップアップの「購読中止日」欄を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>案内メッセージの表示を確認する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="11" t="n"/>
+      <c r="X60" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ポップアップ「購読中止」が表示されること（従来の `既に解約予約されています。…` 警告は表示されず、ポップアップが開くこと）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">終了月ピッカーに `2030/07` が設定されていること（予約中の購読中止日 2030-07-31 の年月）。クリア（×）ボタンが表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ACSMS-MSG-014-016 `解約予約中です。終了月を選び直すと予約を変更し、空にすると予約を取り消します。` が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・予約行は未来日で有効行にならないが、購読中止日のみ予約時点で `t_dokusya.dokusya_chushi_date` へ反映されるため、詳細取得の値から復元できる（API設計書 v1.5）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・紙版（購読種別=1）は従来どおりポップアップを開かず ACSMS-MSG-014-014 を表示すること</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y60" s="10" t="n"/>
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
+      <c r="AB60" s="10" t="n"/>
+      <c r="AC60" s="10" t="n"/>
+      <c r="AD60" s="11" t="n"/>
+      <c r="AE60" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF60" s="11" t="n"/>
+      <c r="AG60" s="45" t="inlineStr"/>
+      <c r="AH60" s="10" t="n"/>
+      <c r="AI60" s="11" t="n"/>
+      <c r="AJ60" s="45" t="inlineStr"/>
+      <c r="AK60" s="10" t="n"/>
+      <c r="AL60" s="11" t="n"/>
+      <c r="AM60" s="45" t="inlineStr"/>
+      <c r="AN60" s="10" t="n"/>
+      <c r="AO60" s="11" t="n"/>
+      <c r="AP60" s="45" t="inlineStr"/>
+      <c r="AQ60" s="10" t="n"/>
+      <c r="AR60" s="11" t="n"/>
+      <c r="AS60" s="45" t="inlineStr"/>
+      <c r="AT60" s="10" t="n"/>
+      <c r="AU60" s="11" t="n"/>
+      <c r="AV60" s="45" t="inlineStr"/>
+      <c r="AW60" s="10" t="n"/>
+      <c r="AX60" s="11" t="n"/>
+      <c r="AY60" s="45" t="inlineStr"/>
+      <c r="AZ60" s="10" t="n"/>
+      <c r="BA60" s="11" t="n"/>
+      <c r="BB60" s="45" t="inlineStr"/>
+      <c r="BC60" s="10" t="n"/>
+      <c r="BD60" s="11" t="n"/>
+      <c r="BE60" s="45" t="inlineStr"/>
+      <c r="BF60" s="10" t="n"/>
+      <c r="BG60" s="11" t="n"/>
+      <c r="BH60" s="45" t="inlineStr"/>
+      <c r="BI60" s="10" t="n"/>
+      <c r="BJ60" s="11" t="n"/>
+      <c r="BK60" s="46" t="inlineStr"/>
+      <c r="BL60" s="10" t="n"/>
+      <c r="BM60" s="10" t="n"/>
+      <c r="BN60" s="10" t="n"/>
+      <c r="BO60" s="10" t="n"/>
+      <c r="BP60" s="10" t="n"/>
+      <c r="BQ60" s="11" t="n"/>
+    </row>
+    <row r="61" ht="450" customHeight="1">
+      <c r="A61" s="44" t="n">
+        <v>45</v>
+      </c>
+      <c r="B61" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-014-045</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="46" t="inlineStr">
+        <is>
+          <t>購読中止 — 電子版：終了月を選び直して予約を変更する</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="11" t="n"/>
+      <c r="J61" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・事前データ：ACSMS-TC-014-044 と同じ（2030/07 の解約予約あり）
+・電子版連携（DENSHIBAN_PUSH_ENABLED=true）が有効</t>
+        </is>
+      </c>
+      <c r="K61" s="10" t="n"/>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="11" t="n"/>
+      <c r="Q61" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「購読中止」ポップアップで終了月を `2030/09` に変更し「確認」をクリックする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DB 確認: `SELECT rireki_no, dokusya_chushi_date, torikeshi_flg, kaiyaku_flg FROM t_dokusya_rireki WHERE dokusya_id = 1020 ORDER BY rireki_no`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DB 確認: `SELECT dokusya_chushi_date FROM t_dokusya WHERE dokusya_id = 1020`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">電子版連携ログを確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DB 確認: `SELECT gamen_name, operation, target_table FROM t_log WHERE target_id = 1020 ORDER BY log_id DESC LIMIT 1`</t>
+          </r>
+        </is>
+      </c>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="10" t="n"/>
+      <c r="T61" s="10" t="n"/>
+      <c r="U61" s="10" t="n"/>
+      <c r="V61" s="10" t="n"/>
+      <c r="W61" s="11" t="n"/>
+      <c r="X61" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">トースト ACSMS-MSG-014-018 `購読停止を予約しました。` が表示され、ポップアップが閉じて一覧が再取得されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">旧予約行の `torikeshi_flg` が `true` になり、打ち消し行（`torikeshi_flg=true`）が1件追加されていること。さらに `dokusya_chushi_date='2030-09-30'`・`kaiyaku_flg=false`・`torikeshi_flg=false` の新しい予約行が1件追加されていること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`dokusya_chushi_date` が `2030-09-30` に更新されていること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`action_kbn=cancel`・`cancel_ym=203009` で電子版へ連携されていること（1回のみ）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`gamen_name='購読者明細検索画面 (ACSMS-SCR-014)'`・`operation='UPDATE'`・`target_table='t_dokusya'` の操作ログが記録されていること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・旧予約の無効化・新予約の挿入・電子版連携・操作ログは単一トランザクション（API設計書「処理手順 4.5／4.5.1」準拠）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・予約中と同じ終了月のまま「確認」した場合は ACSMS-MSG-014-017 `変更がありません。` を表示し、APIを呼ばないこと</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y61" s="10" t="n"/>
+      <c r="Z61" s="10" t="n"/>
+      <c r="AA61" s="10" t="n"/>
+      <c r="AB61" s="10" t="n"/>
+      <c r="AC61" s="10" t="n"/>
+      <c r="AD61" s="11" t="n"/>
+      <c r="AE61" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF61" s="11" t="n"/>
+      <c r="AG61" s="45" t="inlineStr"/>
+      <c r="AH61" s="10" t="n"/>
+      <c r="AI61" s="11" t="n"/>
+      <c r="AJ61" s="45" t="inlineStr"/>
+      <c r="AK61" s="10" t="n"/>
+      <c r="AL61" s="11" t="n"/>
+      <c r="AM61" s="45" t="inlineStr"/>
+      <c r="AN61" s="10" t="n"/>
+      <c r="AO61" s="11" t="n"/>
+      <c r="AP61" s="45" t="inlineStr"/>
+      <c r="AQ61" s="10" t="n"/>
+      <c r="AR61" s="11" t="n"/>
+      <c r="AS61" s="45" t="inlineStr"/>
+      <c r="AT61" s="10" t="n"/>
+      <c r="AU61" s="11" t="n"/>
+      <c r="AV61" s="45" t="inlineStr"/>
+      <c r="AW61" s="10" t="n"/>
+      <c r="AX61" s="11" t="n"/>
+      <c r="AY61" s="45" t="inlineStr"/>
+      <c r="AZ61" s="10" t="n"/>
+      <c r="BA61" s="11" t="n"/>
+      <c r="BB61" s="45" t="inlineStr"/>
+      <c r="BC61" s="10" t="n"/>
+      <c r="BD61" s="11" t="n"/>
+      <c r="BE61" s="45" t="inlineStr"/>
+      <c r="BF61" s="10" t="n"/>
+      <c r="BG61" s="11" t="n"/>
+      <c r="BH61" s="45" t="inlineStr"/>
+      <c r="BI61" s="10" t="n"/>
+      <c r="BJ61" s="11" t="n"/>
+      <c r="BK61" s="46" t="inlineStr"/>
+      <c r="BL61" s="10" t="n"/>
+      <c r="BM61" s="10" t="n"/>
+      <c r="BN61" s="10" t="n"/>
+      <c r="BO61" s="10" t="n"/>
+      <c r="BP61" s="10" t="n"/>
+      <c r="BQ61" s="11" t="n"/>
+    </row>
+    <row r="62" ht="450" customHeight="1">
+      <c r="A62" s="44" t="n">
+        <v>46</v>
+      </c>
+      <c r="B62" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-014-046</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="46" t="inlineStr">
+        <is>
+          <t>購読中止 — 電子版：終了月をクリアして予約を取り消す</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="11" t="n"/>
+      <c r="J62" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・事前データ：ACSMS-TC-014-044 と同じ（2030/07 の解約予約あり）
+・電子版連携（DENSHIBAN_PUSH_ENABLED=true）が有効</t>
+        </is>
+      </c>
+      <c r="K62" s="10" t="n"/>
+      <c r="L62" s="10" t="n"/>
+      <c r="M62" s="10" t="n"/>
+      <c r="N62" s="10" t="n"/>
+      <c r="O62" s="10" t="n"/>
+      <c r="P62" s="11" t="n"/>
+      <c r="Q62" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「購読中止」ポップアップで終了月のクリア（×）をクリックし、欄を空にして「確認」をクリックする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DB 確認: `SELECT rireki_no, dokusya_chushi_date, torikeshi_flg FROM t_dokusya_rireki WHERE dokusya_id = 1020 ORDER BY rireki_no`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DB 確認: `SELECT dokusya_chushi_date, tetsuzuki_shurui FROM t_dokusya WHERE dokusya_id = 1020`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">電子版連携ログを確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>一覧の「購読中止日」列を確認する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R62" s="10" t="n"/>
+      <c r="S62" s="10" t="n"/>
+      <c r="T62" s="10" t="n"/>
+      <c r="U62" s="10" t="n"/>
+      <c r="V62" s="10" t="n"/>
+      <c r="W62" s="11" t="n"/>
+      <c r="X62" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">トースト ACSMS-MSG-014-019 `購読中止を取り消しました。` が表示され、ポップアップが閉じて一覧が再取得されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">旧予約行の `torikeshi_flg` が `true` になり、打ち消し行（`torikeshi_flg=true`）が1件追加されていること。新しい予約行は追加されていないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`dokusya_chushi_date` が `NULL` に戻り、`tetsuzuki_shurui` は `1`（新規＝購読中）のままであること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`action_kbn=cancel`・`cancel_ym=`（空文字）で電子版へ連携されていること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">該当行の「購読中止日」が空欄になっていること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・電子版APIには解約取消専用の処理区分が無いため、`cancel` + 空の `cancel_ym` を送る（顧客判断 2026-08）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・電子版が当該リクエストを拒否した場合は履歴・master・操作ログすべてロールバックされ、電子版が返した理由がポップアップ内に表示されること（クラウド側だけ取消済みにならないこと）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・予約が無い状態で空欄のまま「確認」した場合は ACSMS-MSG-014-020 が返ること</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y62" s="10" t="n"/>
+      <c r="Z62" s="10" t="n"/>
+      <c r="AA62" s="10" t="n"/>
+      <c r="AB62" s="10" t="n"/>
+      <c r="AC62" s="10" t="n"/>
+      <c r="AD62" s="11" t="n"/>
+      <c r="AE62" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF62" s="11" t="n"/>
+      <c r="AG62" s="45" t="inlineStr"/>
+      <c r="AH62" s="10" t="n"/>
+      <c r="AI62" s="11" t="n"/>
+      <c r="AJ62" s="45" t="inlineStr"/>
+      <c r="AK62" s="10" t="n"/>
+      <c r="AL62" s="11" t="n"/>
+      <c r="AM62" s="45" t="inlineStr"/>
+      <c r="AN62" s="10" t="n"/>
+      <c r="AO62" s="11" t="n"/>
+      <c r="AP62" s="45" t="inlineStr"/>
+      <c r="AQ62" s="10" t="n"/>
+      <c r="AR62" s="11" t="n"/>
+      <c r="AS62" s="45" t="inlineStr"/>
+      <c r="AT62" s="10" t="n"/>
+      <c r="AU62" s="11" t="n"/>
+      <c r="AV62" s="45" t="inlineStr"/>
+      <c r="AW62" s="10" t="n"/>
+      <c r="AX62" s="11" t="n"/>
+      <c r="AY62" s="45" t="inlineStr"/>
+      <c r="AZ62" s="10" t="n"/>
+      <c r="BA62" s="11" t="n"/>
+      <c r="BB62" s="45" t="inlineStr"/>
+      <c r="BC62" s="10" t="n"/>
+      <c r="BD62" s="11" t="n"/>
+      <c r="BE62" s="45" t="inlineStr"/>
+      <c r="BF62" s="10" t="n"/>
+      <c r="BG62" s="11" t="n"/>
+      <c r="BH62" s="45" t="inlineStr"/>
+      <c r="BI62" s="10" t="n"/>
+      <c r="BJ62" s="11" t="n"/>
+      <c r="BK62" s="46" t="inlineStr"/>
+      <c r="BL62" s="10" t="n"/>
+      <c r="BM62" s="10" t="n"/>
+      <c r="BN62" s="10" t="n"/>
+      <c r="BO62" s="10" t="n"/>
+      <c r="BP62" s="10" t="n"/>
+      <c r="BQ62" s="11" t="n"/>
+    </row>
+    <row r="63" ht="450" customHeight="1">
+      <c r="A63" s="44" t="n">
+        <v>47</v>
+      </c>
+      <c r="B63" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-014-047</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="46" t="inlineStr">
+        <is>
+          <t>購読中止 — 解約確定後は変更・取消できない</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="11" t="n"/>
+      <c r="J63" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・事前データ：電子版購読者（`dokusya_id=1021, dokusya_shubetsu=2`）の解約が到来日バッチで確定済（`kaiyaku_flg=true` の実解約行あり・`tetsuzuki_shurui=0`）</t>
+        </is>
+      </c>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="11" t="n"/>
+      <c r="Q63" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">検索結果で該当行の「購読中止」リンクの状態を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DevTools で POST `/api/v1/dokusya/1021/stop`（body: `{"dokusya_chushi_date": "2030-09-30"}`）を直接呼び出す
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DevTools で POST `/api/v1/dokusya/1021/stop`（body: `{"dokusya_chushi_date": ""}`）を直接呼び出す
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DB 確認: `SELECT COUNT(*) FROM t_dokusya_rireki WHERE dokusya_id = 1021`</t>
+          </r>
+        </is>
+      </c>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="10" t="n"/>
+      <c r="T63" s="10" t="n"/>
+      <c r="U63" s="10" t="n"/>
+      <c r="V63" s="10" t="n"/>
+      <c r="W63" s="11" t="n"/>
+      <c r="X63" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「購読中止」リンクが非活性であること（手続種類=0:解約のため）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: VALIDATION_ERROR`、`errors[0].message` が ACSMS-MSG-014-015 `解約が確定済みのため変更できません。再購読は購読者編集画面から行ってください。`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2と同じ400が返却されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">履歴の件数が呼び出し前後で変化していないこと（行が追加・取消されていないこと）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・確定済み判定は解約予約行ではなく `kaiyaku_flg=true` を持つ実解約行の有無で行う（API設計書「処理手順 4.4」準拠）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・復帰は購読者編集画面（SCR-011）の再購読で行う
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・フロントエンド側でリンクが非活性となるが、バックエンド側でも直接呼び出しを拒否すること（観点 VP-C-05）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y63" s="10" t="n"/>
+      <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="10" t="n"/>
+      <c r="AB63" s="10" t="n"/>
+      <c r="AC63" s="10" t="n"/>
+      <c r="AD63" s="11" t="n"/>
+      <c r="AE63" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF63" s="11" t="n"/>
+      <c r="AG63" s="45" t="inlineStr"/>
+      <c r="AH63" s="10" t="n"/>
+      <c r="AI63" s="11" t="n"/>
+      <c r="AJ63" s="45" t="inlineStr"/>
+      <c r="AK63" s="10" t="n"/>
+      <c r="AL63" s="11" t="n"/>
+      <c r="AM63" s="45" t="inlineStr"/>
+      <c r="AN63" s="10" t="n"/>
+      <c r="AO63" s="11" t="n"/>
+      <c r="AP63" s="45" t="inlineStr"/>
+      <c r="AQ63" s="10" t="n"/>
+      <c r="AR63" s="11" t="n"/>
+      <c r="AS63" s="45" t="inlineStr"/>
+      <c r="AT63" s="10" t="n"/>
+      <c r="AU63" s="11" t="n"/>
+      <c r="AV63" s="45" t="inlineStr"/>
+      <c r="AW63" s="10" t="n"/>
+      <c r="AX63" s="11" t="n"/>
+      <c r="AY63" s="45" t="inlineStr"/>
+      <c r="AZ63" s="10" t="n"/>
+      <c r="BA63" s="11" t="n"/>
+      <c r="BB63" s="45" t="inlineStr"/>
+      <c r="BC63" s="10" t="n"/>
+      <c r="BD63" s="11" t="n"/>
+      <c r="BE63" s="45" t="inlineStr"/>
+      <c r="BF63" s="10" t="n"/>
+      <c r="BG63" s="11" t="n"/>
+      <c r="BH63" s="45" t="inlineStr"/>
+      <c r="BI63" s="10" t="n"/>
+      <c r="BJ63" s="11" t="n"/>
+      <c r="BK63" s="46" t="inlineStr"/>
+      <c r="BL63" s="10" t="n"/>
+      <c r="BM63" s="10" t="n"/>
+      <c r="BN63" s="10" t="n"/>
+      <c r="BO63" s="10" t="n"/>
+      <c r="BP63" s="10" t="n"/>
+      <c r="BQ63" s="11" t="n"/>
+    </row>
+    <row r="64" ht="450" customHeight="1">
+      <c r="A64" s="44" t="n">
+        <v>48</v>
+      </c>
+      <c r="B64" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-014-048</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="46" t="inlineStr">
+        <is>
+          <t>購読中止 — 最終確認ダイアログ（はい／いいえ）</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="11" t="n"/>
+      <c r="J64" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・事前データ：紙版購読者（`dokusya_id=1022, dokusya_shubetsu=1`／解約予約なし）、電子版購読者（`dokusya_id=1020, dokusya_shubetsu=2, seikyu_kaishi_month='202604'`／2030/07 の解約予約あり）</t>
+        </is>
+      </c>
+      <c r="K64" s="10" t="n"/>
+      <c r="L64" s="10" t="n"/>
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="10" t="n"/>
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="11" t="n"/>
+      <c r="Q64" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">紙版（1022）の「購読中止」ポップアップで購読中止日に `2030/09/15` を選び「確認」をクリックする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">確認ダイアログで「いいえ」をクリックする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">再度「確認」をクリックし、確認ダイアログで「はい」をクリックする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">電子版（1020）の「購読中止」ポップアップで終了月を `2030/09` に変更し「確認」をクリックする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">電子版（1020）の「購読中止」ポップアップで終了月をクリアして「確認」をクリックする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>電子版（1020）の「購読中止」ポップアップで予約中と同じ終了月のまま「確認」をクリックする</t>
+          </r>
+        </is>
+      </c>
+      <c r="R64" s="10" t="n"/>
+      <c r="S64" s="10" t="n"/>
+      <c r="T64" s="10" t="n"/>
+      <c r="U64" s="10" t="n"/>
+      <c r="V64" s="10" t="n"/>
+      <c r="W64" s="11" t="n"/>
+      <c r="X64" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">確認ダイアログ「購読中止確認」が表示されること。本文が ACSMS-MSG-014-021 `2030/09/15で購読を中止します。よろしいですか？`、ボタンが「はい」（赤）／「いいえ」であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">APIが呼ばれないこと。購読中止ポップアップが再表示され、選択した `2030/09/15` が保持されていること（確認ダイアログの表示中はポップアップが隠れていること）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">APIが呼ばれ、ACSMS-MSG-014-018 が表示されてポップアップが閉じること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">本文が ACSMS-MSG-014-022 `購読中止日を2030/09の月末（2030/09/30）に変更します。よろしいですか？` であること（電子版は選択月と実際に止まる日の両方が示されること）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">本文が ACSMS-MSG-014-023 `購読中止の予約を取り消します。よろしいですか？` であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">確認ダイアログが表示されないこと。ACSMS-MSG-014-017 `変更がありません。` がポップアップ内に表示され、APIも呼ばれないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・確認ダイアログは入力チェック（選択範囲・無変更）を通過した後にのみ表示する。「はい」を押した後にフォームエラーで弾かれないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・確認ダイアログ表示中は購読中止ポップアップを非表示にする。「いいえ」「✕」「ESC」「マスククリック」いずれでも選択内容を保ったまま再表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・APIがエラーを返した場合も購読中止ポップアップが再表示され、エラー内容が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・ボタンラベルは プロジェクト共通の はい／いいえ（破壊的意図は赤ボタンで示す・`.claude/rules/vue.md §Modal Confirmation`）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y64" s="10" t="n"/>
+      <c r="Z64" s="10" t="n"/>
+      <c r="AA64" s="10" t="n"/>
+      <c r="AB64" s="10" t="n"/>
+      <c r="AC64" s="10" t="n"/>
+      <c r="AD64" s="11" t="n"/>
+      <c r="AE64" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF64" s="11" t="n"/>
+      <c r="AG64" s="45" t="inlineStr"/>
+      <c r="AH64" s="10" t="n"/>
+      <c r="AI64" s="11" t="n"/>
+      <c r="AJ64" s="45" t="inlineStr"/>
+      <c r="AK64" s="10" t="n"/>
+      <c r="AL64" s="11" t="n"/>
+      <c r="AM64" s="45" t="inlineStr"/>
+      <c r="AN64" s="10" t="n"/>
+      <c r="AO64" s="11" t="n"/>
+      <c r="AP64" s="45" t="inlineStr"/>
+      <c r="AQ64" s="10" t="n"/>
+      <c r="AR64" s="11" t="n"/>
+      <c r="AS64" s="45" t="inlineStr"/>
+      <c r="AT64" s="10" t="n"/>
+      <c r="AU64" s="11" t="n"/>
+      <c r="AV64" s="45" t="inlineStr"/>
+      <c r="AW64" s="10" t="n"/>
+      <c r="AX64" s="11" t="n"/>
+      <c r="AY64" s="45" t="inlineStr"/>
+      <c r="AZ64" s="10" t="n"/>
+      <c r="BA64" s="11" t="n"/>
+      <c r="BB64" s="45" t="inlineStr"/>
+      <c r="BC64" s="10" t="n"/>
+      <c r="BD64" s="11" t="n"/>
+      <c r="BE64" s="45" t="inlineStr"/>
+      <c r="BF64" s="10" t="n"/>
+      <c r="BG64" s="11" t="n"/>
+      <c r="BH64" s="45" t="inlineStr"/>
+      <c r="BI64" s="10" t="n"/>
+      <c r="BJ64" s="11" t="n"/>
+      <c r="BK64" s="46" t="inlineStr"/>
+      <c r="BL64" s="10" t="n"/>
+      <c r="BM64" s="10" t="n"/>
+      <c r="BN64" s="10" t="n"/>
+      <c r="BO64" s="10" t="n"/>
+      <c r="BP64" s="10" t="n"/>
+      <c r="BQ64" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="802">
+  <mergeCells count="887">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
+    <mergeCell ref="B60:D60"/>
     <mergeCell ref="Q27:W27"/>
     <mergeCell ref="AS46:AU46"/>
     <mergeCell ref="BK58:BQ58"/>
@@ -18079,15 +19491,20 @@
     <mergeCell ref="AE41:AF41"/>
     <mergeCell ref="AV57:AX57"/>
     <mergeCell ref="B53:D53"/>
+    <mergeCell ref="AP60:AR60"/>
     <mergeCell ref="E39:I39"/>
     <mergeCell ref="E14:I14"/>
+    <mergeCell ref="AS61:AU61"/>
     <mergeCell ref="W7:Y7"/>
+    <mergeCell ref="AM64:AO64"/>
     <mergeCell ref="AS48:AU48"/>
+    <mergeCell ref="J62:P62"/>
     <mergeCell ref="BK16:BQ16"/>
     <mergeCell ref="AE56:AF56"/>
     <mergeCell ref="AE43:AF43"/>
     <mergeCell ref="AM30:AO30"/>
     <mergeCell ref="AP45:AR45"/>
+    <mergeCell ref="J64:P64"/>
     <mergeCell ref="BE13:BG13"/>
     <mergeCell ref="W8:Y8"/>
     <mergeCell ref="Q37:W37"/>
@@ -18132,6 +19549,7 @@
     <mergeCell ref="AG37:AI37"/>
     <mergeCell ref="J39:P39"/>
     <mergeCell ref="X21:AD21"/>
+    <mergeCell ref="AE62:AF62"/>
     <mergeCell ref="AG47:AI47"/>
     <mergeCell ref="AF8:AH8"/>
     <mergeCell ref="BB27:BD27"/>
@@ -18141,6 +19559,9 @@
     <mergeCell ref="BH34:BJ34"/>
     <mergeCell ref="X23:AD23"/>
     <mergeCell ref="BE38:BG38"/>
+    <mergeCell ref="AE64:AF64"/>
+    <mergeCell ref="AS62:AU62"/>
+    <mergeCell ref="AV63:AX63"/>
     <mergeCell ref="BH49:BJ49"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AP53:AR53"/>
@@ -18148,8 +19569,11 @@
     <mergeCell ref="AP28:AR28"/>
     <mergeCell ref="AE57:AF57"/>
     <mergeCell ref="BK53:BQ53"/>
+    <mergeCell ref="BH60:BJ60"/>
     <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="AS64:AU64"/>
     <mergeCell ref="BE15:BG15"/>
+    <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="BE33:BG33"/>
     <mergeCell ref="BB37:BD37"/>
     <mergeCell ref="AG50:AI50"/>
@@ -18165,8 +19589,10 @@
     <mergeCell ref="AM24:AO24"/>
     <mergeCell ref="AG27:AI27"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="AM60:AO60"/>
     <mergeCell ref="BB38:BD38"/>
     <mergeCell ref="AV14:AX14"/>
+    <mergeCell ref="Q61:W61"/>
     <mergeCell ref="W3:AH3"/>
     <mergeCell ref="E33:I33"/>
     <mergeCell ref="Q48:W48"/>
@@ -18224,6 +19650,7 @@
     <mergeCell ref="Q36:W36"/>
     <mergeCell ref="BE54:BG54"/>
     <mergeCell ref="Q30:W30"/>
+    <mergeCell ref="AE63:AF63"/>
     <mergeCell ref="W1:AH1"/>
     <mergeCell ref="AC8:AE8"/>
     <mergeCell ref="AP44:AR44"/>
@@ -18234,17 +19661,22 @@
     <mergeCell ref="J33:P33"/>
     <mergeCell ref="AE58:AF58"/>
     <mergeCell ref="BB59:BD59"/>
+    <mergeCell ref="AM63:AO63"/>
     <mergeCell ref="X27:AD27"/>
     <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="BE57:BG57"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="AY60:BA60"/>
+    <mergeCell ref="BB61:BD61"/>
     <mergeCell ref="AV15:AX15"/>
     <mergeCell ref="AY16:BA16"/>
+    <mergeCell ref="Q62:W62"/>
     <mergeCell ref="E34:I34"/>
     <mergeCell ref="BB48:BD48"/>
     <mergeCell ref="AG43:AI43"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="E49:I49"/>
+    <mergeCell ref="Q64:W64"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="AY45:BA45"/>
     <mergeCell ref="E36:I36"/>
@@ -18270,6 +19702,7 @@
     <mergeCell ref="BE44:BG44"/>
     <mergeCell ref="AP19:AR19"/>
     <mergeCell ref="AJ57:AL57"/>
+    <mergeCell ref="AG61:AI61"/>
     <mergeCell ref="BE31:BG31"/>
     <mergeCell ref="J21:P21"/>
     <mergeCell ref="A1:E1"/>
@@ -18286,6 +19719,7 @@
     <mergeCell ref="BK44:BQ44"/>
     <mergeCell ref="AY48:BA48"/>
     <mergeCell ref="BB49:BD49"/>
+    <mergeCell ref="AG62:AI62"/>
     <mergeCell ref="AE33:AF33"/>
     <mergeCell ref="BB36:BD36"/>
     <mergeCell ref="X40:AD40"/>
@@ -18303,6 +19737,7 @@
     <mergeCell ref="AY37:BA37"/>
     <mergeCell ref="J49:P49"/>
     <mergeCell ref="J36:P36"/>
+    <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
     <mergeCell ref="AV21:AX21"/>
@@ -18314,8 +19749,10 @@
     <mergeCell ref="BH53:BJ53"/>
     <mergeCell ref="AV29:AX29"/>
     <mergeCell ref="A8:G8"/>
+    <mergeCell ref="BB64:BD64"/>
     <mergeCell ref="AV23:AX23"/>
     <mergeCell ref="BB51:BD51"/>
+    <mergeCell ref="AP63:AR63"/>
     <mergeCell ref="E42:I42"/>
     <mergeCell ref="AY55:BA55"/>
     <mergeCell ref="X59:AD59"/>
@@ -18343,7 +19780,9 @@
     <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="BE53:BG53"/>
+    <mergeCell ref="AJ60:AL60"/>
     <mergeCell ref="AM32:AO32"/>
+    <mergeCell ref="AG64:AI64"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="J24:P24"/>
     <mergeCell ref="AG51:AI51"/>
@@ -18354,6 +19793,7 @@
     <mergeCell ref="E57:I57"/>
     <mergeCell ref="AV50:AX50"/>
     <mergeCell ref="B46:D46"/>
+    <mergeCell ref="Q60:W60"/>
     <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="E32:I32"/>
     <mergeCell ref="AS41:AU41"/>
@@ -18369,17 +19809,20 @@
     <mergeCell ref="AP38:AR38"/>
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="AS43:AU43"/>
+    <mergeCell ref="AY63:BA63"/>
     <mergeCell ref="BE25:BG25"/>
     <mergeCell ref="BK38:BQ38"/>
     <mergeCell ref="F4:AH4"/>
     <mergeCell ref="X51:AD51"/>
     <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="BH61:BJ61"/>
     <mergeCell ref="AG17:AI17"/>
     <mergeCell ref="AS36:AU36"/>
     <mergeCell ref="J50:P50"/>
     <mergeCell ref="AM39:AO39"/>
     <mergeCell ref="AP40:AR40"/>
     <mergeCell ref="J42:P42"/>
+    <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="AG19:AI19"/>
@@ -18387,8 +19830,11 @@
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="Q25:W25"/>
     <mergeCell ref="AV37:AX37"/>
+    <mergeCell ref="E60:I60"/>
     <mergeCell ref="J37:P37"/>
+    <mergeCell ref="AV60:AX60"/>
     <mergeCell ref="Q33:W33"/>
+    <mergeCell ref="X61:AD61"/>
     <mergeCell ref="BK27:BQ27"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="AE29:AF29"/>
@@ -18399,6 +19845,7 @@
     <mergeCell ref="E45:I45"/>
     <mergeCell ref="AS29:AU29"/>
     <mergeCell ref="AM42:AO42"/>
+    <mergeCell ref="X62:AD62"/>
     <mergeCell ref="AE37:AF37"/>
     <mergeCell ref="BH16:BJ16"/>
     <mergeCell ref="AM29:AO29"/>
@@ -18409,10 +19856,13 @@
     <mergeCell ref="AV27:AX27"/>
     <mergeCell ref="BE55:BG55"/>
     <mergeCell ref="AS31:AU31"/>
+    <mergeCell ref="X64:AD64"/>
     <mergeCell ref="J32:P32"/>
+    <mergeCell ref="J63:P63"/>
     <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
     <mergeCell ref="BB58:BD58"/>
+    <mergeCell ref="B61:D61"/>
     <mergeCell ref="J47:P47"/>
     <mergeCell ref="AV58:AX58"/>
     <mergeCell ref="BB20:BD20"/>
@@ -18421,6 +19871,7 @@
     <mergeCell ref="AJ28:AL28"/>
     <mergeCell ref="BK17:BQ17"/>
     <mergeCell ref="BK55:BQ55"/>
+    <mergeCell ref="BB60:BD60"/>
     <mergeCell ref="AP30:AR30"/>
     <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="AJ30:AL30"/>
@@ -18433,12 +19884,15 @@
     <mergeCell ref="AY19:BA19"/>
     <mergeCell ref="BK25:BQ25"/>
     <mergeCell ref="Q21:W21"/>
+    <mergeCell ref="AP61:AR61"/>
     <mergeCell ref="AM16:AO16"/>
     <mergeCell ref="AP48:AR48"/>
+    <mergeCell ref="B64:D64"/>
     <mergeCell ref="AE44:AF44"/>
     <mergeCell ref="X57:AD57"/>
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="AP41:AR41"/>
+    <mergeCell ref="J60:P60"/>
     <mergeCell ref="BK41:BQ41"/>
     <mergeCell ref="BB13:BD13"/>
     <mergeCell ref="AM17:AO17"/>
@@ -18492,17 +19946,21 @@
     <mergeCell ref="AJ29:AL29"/>
     <mergeCell ref="AG33:AI33"/>
     <mergeCell ref="X17:AD17"/>
+    <mergeCell ref="BK61:BQ61"/>
     <mergeCell ref="AJ44:AL44"/>
     <mergeCell ref="Q54:W54"/>
     <mergeCell ref="AY27:BA27"/>
     <mergeCell ref="AJ31:AL31"/>
+    <mergeCell ref="B62:D62"/>
     <mergeCell ref="Q29:W29"/>
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="X19:AD19"/>
+    <mergeCell ref="AE60:AF60"/>
     <mergeCell ref="AS58:AU58"/>
     <mergeCell ref="AG34:AI34"/>
     <mergeCell ref="AV59:AX59"/>
+    <mergeCell ref="AP62:AR62"/>
     <mergeCell ref="E16:I16"/>
     <mergeCell ref="AV46:AX46"/>
     <mergeCell ref="Q31:W31"/>
@@ -18510,15 +19968,22 @@
     <mergeCell ref="AS50:AU50"/>
     <mergeCell ref="E10:I11"/>
     <mergeCell ref="BK56:BQ56"/>
+    <mergeCell ref="BK62:BQ62"/>
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="BH37:BJ37"/>
     <mergeCell ref="AE45:AF45"/>
     <mergeCell ref="X58:AD58"/>
+    <mergeCell ref="AS60:AU60"/>
+    <mergeCell ref="AV61:AX61"/>
+    <mergeCell ref="AP64:AR64"/>
     <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AP51:AR51"/>
     <mergeCell ref="AG59:AI59"/>
+    <mergeCell ref="BK64:BQ64"/>
     <mergeCell ref="BK51:BQ51"/>
+    <mergeCell ref="X60:AD60"/>
+    <mergeCell ref="AM61:AO61"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="BB54:BD54"/>
     <mergeCell ref="AE59:AF59"/>
@@ -18531,6 +19996,7 @@
     <mergeCell ref="AM20:AO20"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="B19:D19"/>
+    <mergeCell ref="J61:P61"/>
     <mergeCell ref="AY11:BA11"/>
     <mergeCell ref="Q57:W57"/>
     <mergeCell ref="J48:P48"/>
@@ -18591,17 +20057,22 @@
     <mergeCell ref="E19:I19"/>
     <mergeCell ref="BK21:BQ21"/>
     <mergeCell ref="BB56:BD56"/>
+    <mergeCell ref="AE61:AF61"/>
+    <mergeCell ref="AV64:AX64"/>
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AY30:BA30"/>
     <mergeCell ref="AJ32:AL32"/>
+    <mergeCell ref="AJ63:AL63"/>
     <mergeCell ref="AP25:AR25"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="AY46:BA46"/>
     <mergeCell ref="BB57:BD57"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="Q58:W58"/>
+    <mergeCell ref="AY61:BA61"/>
     <mergeCell ref="AV16:AX16"/>
+    <mergeCell ref="Q63:W63"/>
     <mergeCell ref="AJ40:AL40"/>
     <mergeCell ref="Q50:W50"/>
     <mergeCell ref="AJ27:AL27"/>
@@ -18619,6 +20090,7 @@
     <mergeCell ref="AS21:AU21"/>
     <mergeCell ref="AY43:BA43"/>
     <mergeCell ref="BE32:BG32"/>
+    <mergeCell ref="BE63:BG63"/>
     <mergeCell ref="BK14:BQ14"/>
     <mergeCell ref="AE16:AF16"/>
     <mergeCell ref="AG32:AI32"/>
@@ -18626,6 +20098,7 @@
     <mergeCell ref="BH43:BJ43"/>
     <mergeCell ref="BE47:BG47"/>
     <mergeCell ref="AP22:AR22"/>
+    <mergeCell ref="BK60:BQ60"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="BE40:BG40"/>
     <mergeCell ref="AP15:AR15"/>
@@ -18640,6 +20113,7 @@
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="AJ45:AL45"/>
     <mergeCell ref="AG57:AI57"/>
+    <mergeCell ref="E63:I63"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="AJ55:AL55"/>
     <mergeCell ref="AY34:BA34"/>
@@ -18659,6 +20133,7 @@
     <mergeCell ref="X28:AD28"/>
     <mergeCell ref="AS30:AU30"/>
     <mergeCell ref="BB47:BD47"/>
+    <mergeCell ref="AG60:AI60"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="AS42:AU42"/>
     <mergeCell ref="A35:BQ35"/>
@@ -18676,6 +20151,8 @@
     <mergeCell ref="AJ48:AL48"/>
     <mergeCell ref="AV42:AX42"/>
     <mergeCell ref="BE59:BG59"/>
+    <mergeCell ref="AY62:BA62"/>
+    <mergeCell ref="BB63:BD63"/>
     <mergeCell ref="BE46:BG46"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
@@ -18683,6 +20160,7 @@
     <mergeCell ref="AY28:BA28"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B28:D28"/>
+    <mergeCell ref="AY64:BA64"/>
     <mergeCell ref="AV19:AX19"/>
     <mergeCell ref="AS23:AU23"/>
     <mergeCell ref="E38:I38"/>
@@ -18720,6 +20198,7 @@
     <mergeCell ref="AP23:AR23"/>
     <mergeCell ref="B56:D56"/>
     <mergeCell ref="J20:P20"/>
+    <mergeCell ref="AJ61:AL61"/>
     <mergeCell ref="AV47:AX47"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="BE51:BG51"/>
@@ -18728,6 +20207,7 @@
     <mergeCell ref="BK33:BQ33"/>
     <mergeCell ref="A5:S5"/>
     <mergeCell ref="J22:P22"/>
+    <mergeCell ref="BH62:BJ62"/>
     <mergeCell ref="AV38:AX38"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="AY39:BA39"/>
@@ -18743,6 +20223,7 @@
     <mergeCell ref="BH57:BJ57"/>
     <mergeCell ref="AG13:AI13"/>
     <mergeCell ref="AV33:AX33"/>
+    <mergeCell ref="BE61:BG61"/>
     <mergeCell ref="AP36:AR36"/>
     <mergeCell ref="AS37:AU37"/>
     <mergeCell ref="AE14:AF14"/>
@@ -18759,16 +20240,20 @@
     <mergeCell ref="E59:I59"/>
     <mergeCell ref="E46:I46"/>
     <mergeCell ref="J40:P40"/>
+    <mergeCell ref="BE62:BG62"/>
     <mergeCell ref="J15:P15"/>
     <mergeCell ref="AM41:AO41"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="AY21:BA21"/>
+    <mergeCell ref="E61:I61"/>
+    <mergeCell ref="BE64:BG64"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="X49:AD49"/>
     <mergeCell ref="E54:I54"/>
     <mergeCell ref="AV22:AX22"/>
     <mergeCell ref="AY23:BA23"/>
+    <mergeCell ref="AS63:AU63"/>
     <mergeCell ref="E41:I41"/>
     <mergeCell ref="AE27:AF27"/>
     <mergeCell ref="AP54:AR54"/>
@@ -18778,6 +20263,7 @@
     <mergeCell ref="AP29:AR29"/>
     <mergeCell ref="AV51:AX51"/>
     <mergeCell ref="E43:I43"/>
+    <mergeCell ref="X63:AD63"/>
     <mergeCell ref="BB15:BD15"/>
     <mergeCell ref="BE16:BG16"/>
     <mergeCell ref="AE20:AF20"/>
@@ -18790,6 +20276,7 @@
     <mergeCell ref="AP31:AR31"/>
     <mergeCell ref="BH14:BJ14"/>
     <mergeCell ref="BK54:BQ54"/>
+    <mergeCell ref="AJ62:AL62"/>
     <mergeCell ref="AJ37:AL37"/>
     <mergeCell ref="AY49:BA49"/>
     <mergeCell ref="BE11:BG11"/>
@@ -18798,11 +20285,13 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="Q16:W16"/>
     <mergeCell ref="AV40:AX40"/>
+    <mergeCell ref="AJ64:AL64"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="J28:P28"/>
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="BK49:BQ49"/>
+    <mergeCell ref="B63:D63"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AE38:AF38"/>
     <mergeCell ref="AV54:AX54"/>
@@ -18821,11 +20310,13 @@
     <mergeCell ref="AM14:AO14"/>
     <mergeCell ref="AE15:AF15"/>
     <mergeCell ref="AP42:AR42"/>
+    <mergeCell ref="BH63:BJ63"/>
     <mergeCell ref="AJ42:AL42"/>
     <mergeCell ref="AP58:AR58"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="AM13:AO13"/>
     <mergeCell ref="X55:AD55"/>
+    <mergeCell ref="AM62:AO62"/>
     <mergeCell ref="AJ17:AL17"/>
     <mergeCell ref="AM56:AO56"/>
     <mergeCell ref="J54:P54"/>
@@ -18834,12 +20325,14 @@
     <mergeCell ref="Q44:W44"/>
     <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="E62:I62"/>
     <mergeCell ref="J56:P56"/>
     <mergeCell ref="AY58:BA58"/>
     <mergeCell ref="J43:P43"/>
     <mergeCell ref="AM57:AO57"/>
     <mergeCell ref="X25:AD25"/>
     <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="E64:I64"/>
     <mergeCell ref="E51:I51"/>
     <mergeCell ref="BK31:BQ31"/>
     <mergeCell ref="BE17:BG17"/>
@@ -18850,6 +20343,7 @@
     <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
+    <mergeCell ref="BH64:BJ64"/>
     <mergeCell ref="BE19:BG19"/>
     <mergeCell ref="BK32:BQ32"/>
     <mergeCell ref="AM33:AO33"/>
@@ -18863,21 +20357,23 @@
     <mergeCell ref="AE30:AF30"/>
     <mergeCell ref="AG10:AU10"/>
     <mergeCell ref="AG44:AI44"/>
+    <mergeCell ref="AV62:AX62"/>
     <mergeCell ref="BE14:BG14"/>
     <mergeCell ref="BB24:BD24"/>
     <mergeCell ref="AM28:AO28"/>
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="AV56:AX56"/>
     <mergeCell ref="B58:D58"/>
+    <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE17 AE19:AE25 AE27:AE34 AE36:AE51 AE53:AE59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE17 AE19:AE25 AE27:AE34 AE36:AE51 AE53:AE64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG17 AG19:AG25 AG27:AG34 AG36:AG51 AG53:AG59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG17 AG19:AG25 AG27:AG34 AG36:AG51 AG53:AG64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV17 AV19:AV25 AV27:AV34 AV36:AV51 AV53:AV59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV17 AV19:AV25 AV27:AV34 AV36:AV51 AV53:AV64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/docs/design/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者明細検索画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者明細検索画面_v1.0.xlsx
@@ -6346,7 +6346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ64"/>
+  <dimension ref="A1:BQ67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -18065,220 +18065,74 @@
       <c r="BP59" s="10" t="n"/>
       <c r="BQ59" s="11" t="n"/>
     </row>
-    <row r="60" ht="450" customHeight="1">
-      <c r="A60" s="44" t="n">
-        <v>44</v>
-      </c>
-      <c r="B60" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-014-044</t>
-        </is>
-      </c>
+    <row r="60" ht="22.5" customHeight="1">
+      <c r="A60" s="32" t="inlineStr">
+        <is>
+          <t>購読中止・総部数表示・削除制限（Function — Stop / Total-busu / Delete）</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="n"/>
       <c r="C60" s="10" t="n"/>
-      <c r="D60" s="11" t="n"/>
-      <c r="E60" s="46" t="inlineStr">
-        <is>
-          <t>購読中止 — 電子版：予約中の終了月がポップアップに復元される</t>
-        </is>
-      </c>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
       <c r="F60" s="10" t="n"/>
       <c r="G60" s="10" t="n"/>
       <c r="H60" s="10" t="n"/>
-      <c r="I60" s="11" t="n"/>
-      <c r="J60" s="46" t="inlineStr">
-        <is>
-          <t>・role: JA_HONTEN
-・事前データ：電子版購読者（`dokusya_id=1020, dokusya_shubetsu=2, shiharai_hoho≠6, seikyu_kaishi_month='202604'`）に 2030/07 の解約予約が登録済（到来日バッチ未実行＝`kaiyaku_flg=false`）</t>
-        </is>
-      </c>
+      <c r="I60" s="10" t="n"/>
+      <c r="J60" s="10" t="n"/>
       <c r="K60" s="10" t="n"/>
       <c r="L60" s="10" t="n"/>
       <c r="M60" s="10" t="n"/>
       <c r="N60" s="10" t="n"/>
       <c r="O60" s="10" t="n"/>
-      <c r="P60" s="11" t="n"/>
-      <c r="Q60" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">購読者明細検索画面で該当行の「購読中止」リンクをクリックする
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ポップアップの「購読中止日」欄を確認する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>案内メッセージの表示を確認する</t>
-          </r>
-        </is>
-      </c>
+      <c r="P60" s="10" t="n"/>
+      <c r="Q60" s="10" t="n"/>
       <c r="R60" s="10" t="n"/>
       <c r="S60" s="10" t="n"/>
       <c r="T60" s="10" t="n"/>
       <c r="U60" s="10" t="n"/>
       <c r="V60" s="10" t="n"/>
-      <c r="W60" s="11" t="n"/>
-      <c r="X60" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ポップアップ「購読中止」が表示されること（従来の `既に解約予約されています。…` 警告は表示されず、ポップアップが開くこと）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">終了月ピッカーに `2030/07` が設定されていること（予約中の購読中止日 2030-07-31 の年月）。クリア（×）ボタンが表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ACSMS-MSG-014-016 `解約予約中です。終了月を選び直すと予約を変更し、空にすると予約を取り消します。` が表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・予約行は未来日で有効行にならないが、購読中止日のみ予約時点で `t_dokusya.dokusya_chushi_date` へ反映されるため、詳細取得の値から復元できる（API設計書 v1.5）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・紙版（購読種別=1）は従来どおりポップアップを開かず ACSMS-MSG-014-014 を表示すること</t>
-          </r>
-        </is>
-      </c>
+      <c r="W60" s="10" t="n"/>
+      <c r="X60" s="10" t="n"/>
       <c r="Y60" s="10" t="n"/>
       <c r="Z60" s="10" t="n"/>
       <c r="AA60" s="10" t="n"/>
       <c r="AB60" s="10" t="n"/>
       <c r="AC60" s="10" t="n"/>
-      <c r="AD60" s="11" t="n"/>
-      <c r="AE60" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF60" s="11" t="n"/>
-      <c r="AG60" s="45" t="inlineStr"/>
+      <c r="AD60" s="10" t="n"/>
+      <c r="AE60" s="10" t="n"/>
+      <c r="AF60" s="10" t="n"/>
+      <c r="AG60" s="10" t="n"/>
       <c r="AH60" s="10" t="n"/>
-      <c r="AI60" s="11" t="n"/>
-      <c r="AJ60" s="45" t="inlineStr"/>
+      <c r="AI60" s="10" t="n"/>
+      <c r="AJ60" s="10" t="n"/>
       <c r="AK60" s="10" t="n"/>
-      <c r="AL60" s="11" t="n"/>
-      <c r="AM60" s="45" t="inlineStr"/>
+      <c r="AL60" s="10" t="n"/>
+      <c r="AM60" s="10" t="n"/>
       <c r="AN60" s="10" t="n"/>
-      <c r="AO60" s="11" t="n"/>
-      <c r="AP60" s="45" t="inlineStr"/>
+      <c r="AO60" s="10" t="n"/>
+      <c r="AP60" s="10" t="n"/>
       <c r="AQ60" s="10" t="n"/>
-      <c r="AR60" s="11" t="n"/>
-      <c r="AS60" s="45" t="inlineStr"/>
+      <c r="AR60" s="10" t="n"/>
+      <c r="AS60" s="10" t="n"/>
       <c r="AT60" s="10" t="n"/>
-      <c r="AU60" s="11" t="n"/>
-      <c r="AV60" s="45" t="inlineStr"/>
+      <c r="AU60" s="10" t="n"/>
+      <c r="AV60" s="10" t="n"/>
       <c r="AW60" s="10" t="n"/>
-      <c r="AX60" s="11" t="n"/>
-      <c r="AY60" s="45" t="inlineStr"/>
+      <c r="AX60" s="10" t="n"/>
+      <c r="AY60" s="10" t="n"/>
       <c r="AZ60" s="10" t="n"/>
-      <c r="BA60" s="11" t="n"/>
-      <c r="BB60" s="45" t="inlineStr"/>
+      <c r="BA60" s="10" t="n"/>
+      <c r="BB60" s="10" t="n"/>
       <c r="BC60" s="10" t="n"/>
-      <c r="BD60" s="11" t="n"/>
-      <c r="BE60" s="45" t="inlineStr"/>
+      <c r="BD60" s="10" t="n"/>
+      <c r="BE60" s="10" t="n"/>
       <c r="BF60" s="10" t="n"/>
-      <c r="BG60" s="11" t="n"/>
-      <c r="BH60" s="45" t="inlineStr"/>
+      <c r="BG60" s="10" t="n"/>
+      <c r="BH60" s="10" t="n"/>
       <c r="BI60" s="10" t="n"/>
-      <c r="BJ60" s="11" t="n"/>
-      <c r="BK60" s="46" t="inlineStr"/>
+      <c r="BJ60" s="10" t="n"/>
+      <c r="BK60" s="10" t="n"/>
       <c r="BL60" s="10" t="n"/>
       <c r="BM60" s="10" t="n"/>
       <c r="BN60" s="10" t="n"/>
@@ -18288,18 +18142,18 @@
     </row>
     <row r="61" ht="450" customHeight="1">
       <c r="A61" s="44" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B61" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-014-045</t>
+          <t>ACSMS-TC-014-044</t>
         </is>
       </c>
       <c r="C61" s="10" t="n"/>
       <c r="D61" s="11" t="n"/>
       <c r="E61" s="46" t="inlineStr">
         <is>
-          <t>購読中止 — 電子版：終了月を選び直して予約を変更する</t>
+          <t>購読中止 — 電子版：予約中の終了月がポップアップに復元される</t>
         </is>
       </c>
       <c r="F61" s="10" t="n"/>
@@ -18309,8 +18163,7 @@
       <c r="J61" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN
-・事前データ：ACSMS-TC-014-044 と同じ（2030/07 の解約予約あり）
-・電子版連携（DENSHIBAN_PUSH_ENABLED=true）が有効</t>
+・事前データ：電子版購読者（`dokusya_id=1020, dokusya_shubetsu=2, shiharai_hoho≠6, seikyu_kaishi_month='202604'`）に 2030/07 の解約予約が登録済（到来日バッチ未実行＝`kaiyaku_flg=false`）</t>
         </is>
       </c>
       <c r="K61" s="10" t="n"/>
@@ -18335,7 +18188,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「購読中止」ポップアップで終了月を `2030/09` に変更し「確認」をクリックする
+            <t xml:space="preserve">購読者明細検索画面で該当行の「購読中止」リンクをクリックする
 </t>
           </r>
           <r>
@@ -18352,7 +18205,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DB 確認: `SELECT rireki_no, dokusya_chushi_date, torikeshi_flg, kaiyaku_flg FROM t_dokusya_rireki WHERE dokusya_id = 1020 ORDER BY rireki_no`
+            <t xml:space="preserve">ポップアップの「購読中止日」欄を確認する
 </t>
           </r>
           <r>
@@ -18369,41 +18222,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DB 確認: `SELECT dokusya_chushi_date FROM t_dokusya WHERE dokusya_id = 1020`
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">電子版連携ログを確認する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ5：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>DB 確認: `SELECT gamen_name, operation, target_table FROM t_log WHERE target_id = 1020 ORDER BY log_id DESC LIMIT 1`</t>
+            <t>案内メッセージの表示を確認する</t>
           </r>
         </is>
       </c>
@@ -18429,7 +18248,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">トースト ACSMS-MSG-014-018 `購読停止を予約しました。` が表示され、ポップアップが閉じて一覧が再取得されること
+            <t xml:space="preserve">ポップアップ「購読中止」が表示されること（従来の `既に解約予約されています。…` 警告は表示されず、ポップアップが開くこと）
 </t>
           </r>
           <r>
@@ -18446,7 +18265,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">旧予約行の `torikeshi_flg` が `true` になり、打ち消し行（`torikeshi_flg=true`）が1件追加されていること。さらに `dokusya_chushi_date='2030-09-30'`・`kaiyaku_flg=false`・`torikeshi_flg=false` の新しい予約行が1件追加されていること
+            <t xml:space="preserve">終了月ピッカーに `2030/07` が設定されていること（予約中の購読中止日 2030-07-31 の年月）。クリア（×）ボタンが表示されること
 </t>
           </r>
           <r>
@@ -18463,41 +18282,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">`dokusya_chushi_date` が `2030-09-30` に更新されていること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">`action_kbn=cancel`・`cancel_ym=203009` で電子版へ連携されていること（1回のみ）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ5：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">`gamen_name='購読者明細検索画面 (ACSMS-SCR-014)'`・`operation='UPDATE'`・`target_table='t_dokusya'` の操作ログが記録されていること
+            <t xml:space="preserve">ACSMS-MSG-014-016 `解約予約中です。終了月を選び直すと予約を変更し、空にすると予約を取り消します。` が表示されること
 </t>
           </r>
           <r>
@@ -18514,15 +18299,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・旧予約の無効化・新予約の挿入・電子版連携・操作ログは単一トランザクション（API設計書「処理手順 4.5／4.5.1」準拠）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・予約中と同じ終了月のまま「確認」した場合は ACSMS-MSG-014-017 `変更がありません。` を表示し、APIを呼ばないこと</t>
+            <t xml:space="preserve">・予約行は未来日で有効行にならないが、購読中止日のみ予約時点で `t_dokusya.dokusya_chushi_date` へ反映されるため、詳細取得の値から復元できる（API設計書 v1.5）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・紙版（購読種別=1）は従来どおりポップアップを開かず ACSMS-MSG-014-014 を表示すること</t>
           </r>
         </is>
       </c>
@@ -18578,18 +18363,18 @@
     </row>
     <row r="62" ht="450" customHeight="1">
       <c r="A62" s="44" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B62" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-014-046</t>
+          <t>ACSMS-TC-014-045</t>
         </is>
       </c>
       <c r="C62" s="10" t="n"/>
       <c r="D62" s="11" t="n"/>
       <c r="E62" s="46" t="inlineStr">
         <is>
-          <t>購読中止 — 電子版：終了月をクリアして予約を取り消す</t>
+          <t>購読中止 — 電子版：終了月を選び直して予約を変更する</t>
         </is>
       </c>
       <c r="F62" s="10" t="n"/>
@@ -18625,7 +18410,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「購読中止」ポップアップで終了月のクリア（×）をクリックし、欄を空にして「確認」をクリックする
+            <t xml:space="preserve">「購読中止」ポップアップで終了月を `2030/09` に変更し「確認」をクリックする
 </t>
           </r>
           <r>
@@ -18642,7 +18427,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DB 確認: `SELECT rireki_no, dokusya_chushi_date, torikeshi_flg FROM t_dokusya_rireki WHERE dokusya_id = 1020 ORDER BY rireki_no`
+            <t xml:space="preserve">DB 確認: `SELECT rireki_no, dokusya_chushi_date, torikeshi_flg, kaiyaku_flg FROM t_dokusya_rireki WHERE dokusya_id = 1020 ORDER BY rireki_no`
 </t>
           </r>
           <r>
@@ -18659,7 +18444,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DB 確認: `SELECT dokusya_chushi_date, tetsuzuki_shurui FROM t_dokusya WHERE dokusya_id = 1020`
+            <t xml:space="preserve">DB 確認: `SELECT dokusya_chushi_date FROM t_dokusya WHERE dokusya_id = 1020`
 </t>
           </r>
           <r>
@@ -18693,7 +18478,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>一覧の「購読中止日」列を確認する</t>
+            <t>DB 確認: `SELECT gamen_name, operation, target_table FROM t_log WHERE target_id = 1020 ORDER BY log_id DESC LIMIT 1`</t>
           </r>
         </is>
       </c>
@@ -18719,7 +18504,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">トースト ACSMS-MSG-014-019 `購読中止を取り消しました。` が表示され、ポップアップが閉じて一覧が再取得されること
+            <t xml:space="preserve">トースト ACSMS-MSG-014-018 `購読停止を予約しました。` が表示され、ポップアップが閉じて一覧が再取得されること
 </t>
           </r>
           <r>
@@ -18736,7 +18521,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">旧予約行の `torikeshi_flg` が `true` になり、打ち消し行（`torikeshi_flg=true`）が1件追加されていること。新しい予約行は追加されていないこと
+            <t xml:space="preserve">旧予約行の `torikeshi_flg` が `true` になり、打ち消し行（`torikeshi_flg=true`）が1件追加されていること。さらに `dokusya_chushi_date='2030-09-30'`・`kaiyaku_flg=false`・`torikeshi_flg=false` の新しい予約行が1件追加されていること
 </t>
           </r>
           <r>
@@ -18753,7 +18538,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">`dokusya_chushi_date` が `NULL` に戻り、`tetsuzuki_shurui` は `1`（新規＝購読中）のままであること
+            <t xml:space="preserve">`dokusya_chushi_date` が `2030-09-30` に更新されていること
 </t>
           </r>
           <r>
@@ -18770,7 +18555,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">`action_kbn=cancel`・`cancel_ym=`（空文字）で電子版へ連携されていること
+            <t xml:space="preserve">`action_kbn=cancel`・`cancel_ym=203009` で電子版へ連携されていること（1回のみ）
 </t>
           </r>
           <r>
@@ -18787,7 +18572,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">該当行の「購読中止日」が空欄になっていること
+            <t xml:space="preserve">`gamen_name='購読者明細検索画面 (ACSMS-SCR-014)'`・`operation='UPDATE'`・`target_table='t_dokusya'` の操作ログが記録されていること
 </t>
           </r>
           <r>
@@ -18804,23 +18589,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・電子版APIには解約取消専用の処理区分が無いため、`cancel` + 空の `cancel_ym` を送る（顧客判断 2026-08）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・電子版が当該リクエストを拒否した場合は履歴・master・操作ログすべてロールバックされ、電子版が返した理由がポップアップ内に表示されること（クラウド側だけ取消済みにならないこと）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・予約が無い状態で空欄のまま「確認」した場合は ACSMS-MSG-014-020 が返ること</t>
+            <t xml:space="preserve">・旧予約の無効化・新予約の挿入・電子版連携・操作ログは単一トランザクション（API設計書「処理手順 4.5／4.5.1」準拠）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・予約中と同じ終了月のまま「確認」した場合は ACSMS-MSG-014-017 `変更がありません。` を表示し、APIを呼ばないこと</t>
           </r>
         </is>
       </c>
@@ -18876,18 +18653,18 @@
     </row>
     <row r="63" ht="450" customHeight="1">
       <c r="A63" s="44" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B63" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-014-047</t>
+          <t>ACSMS-TC-014-046</t>
         </is>
       </c>
       <c r="C63" s="10" t="n"/>
       <c r="D63" s="11" t="n"/>
       <c r="E63" s="46" t="inlineStr">
         <is>
-          <t>購読中止 — 解約確定後は変更・取消できない</t>
+          <t>購読中止 — 電子版：終了月をクリアして予約を取り消す</t>
         </is>
       </c>
       <c r="F63" s="10" t="n"/>
@@ -18897,7 +18674,8 @@
       <c r="J63" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN
-・事前データ：電子版購読者（`dokusya_id=1021, dokusya_shubetsu=2`）の解約が到来日バッチで確定済（`kaiyaku_flg=true` の実解約行あり・`tetsuzuki_shurui=0`）</t>
+・事前データ：ACSMS-TC-014-044 と同じ（2030/07 の解約予約あり）
+・電子版連携（DENSHIBAN_PUSH_ENABLED=true）が有効</t>
         </is>
       </c>
       <c r="K63" s="10" t="n"/>
@@ -18922,7 +18700,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">検索結果で該当行の「購読中止」リンクの状態を確認する
+            <t xml:space="preserve">「購読中止」ポップアップで終了月のクリア（×）をクリックし、欄を空にして「確認」をクリックする
 </t>
           </r>
           <r>
@@ -18939,7 +18717,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DevTools で POST `/api/v1/dokusya/1021/stop`（body: `{"dokusya_chushi_date": "2030-09-30"}`）を直接呼び出す
+            <t xml:space="preserve">DB 確認: `SELECT rireki_no, dokusya_chushi_date, torikeshi_flg FROM t_dokusya_rireki WHERE dokusya_id = 1020 ORDER BY rireki_no`
 </t>
           </r>
           <r>
@@ -18956,7 +18734,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DevTools で POST `/api/v1/dokusya/1021/stop`（body: `{"dokusya_chushi_date": ""}`）を直接呼び出す
+            <t xml:space="preserve">DB 確認: `SELECT dokusya_chushi_date, tetsuzuki_shurui FROM t_dokusya WHERE dokusya_id = 1020`
 </t>
           </r>
           <r>
@@ -18973,7 +18751,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DB 確認: `SELECT COUNT(*) FROM t_dokusya_rireki WHERE dokusya_id = 1021`</t>
+            <t xml:space="preserve">電子版連携ログを確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>一覧の「購読中止日」列を確認する</t>
           </r>
         </is>
       </c>
@@ -18999,7 +18794,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「購読中止」リンクが非活性であること（手続種類=0:解約のため）
+            <t xml:space="preserve">トースト ACSMS-MSG-014-019 `購読中止を取り消しました。` が表示され、ポップアップが閉じて一覧が再取得されること
 </t>
           </r>
           <r>
@@ -19016,7 +18811,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: VALIDATION_ERROR`、`errors[0].message` が ACSMS-MSG-014-015 `解約が確定済みのため変更できません。再購読は購読者編集画面から行ってください。`）
+            <t xml:space="preserve">旧予約行の `torikeshi_flg` が `true` になり、打ち消し行（`torikeshi_flg=true`）が1件追加されていること。新しい予約行は追加されていないこと
 </t>
           </r>
           <r>
@@ -19033,7 +18828,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">ステップ2と同じ400が返却されること
+            <t xml:space="preserve">`dokusya_chushi_date` が `NULL` に戻り、`tetsuzuki_shurui` は `1`（新規＝購読中）のままであること
 </t>
           </r>
           <r>
@@ -19050,7 +18845,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">履歴の件数が呼び出し前後で変化していないこと（行が追加・取消されていないこと）
+            <t xml:space="preserve">`action_kbn=cancel`・`cancel_ym=`（空文字）で電子版へ連携されていること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">該当行の「購読中止日」が空欄になっていること
 </t>
           </r>
           <r>
@@ -19067,23 +18879,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・確定済み判定は解約予約行ではなく `kaiyaku_flg=true` を持つ実解約行の有無で行う（API設計書「処理手順 4.4」準拠）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・復帰は購読者編集画面（SCR-011）の再購読で行う
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・フロントエンド側でリンクが非活性となるが、バックエンド側でも直接呼び出しを拒否すること（観点 VP-C-05）</t>
+            <t xml:space="preserve">・電子版APIには解約取消専用の処理区分が無いため、`cancel` + 空の `cancel_ym` を送る（顧客判断 2026-08）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・電子版が当該リクエストを拒否した場合は履歴・master・操作ログすべてロールバックされ、電子版が返した理由がポップアップ内に表示されること（クラウド側だけ取消済みにならないこと）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・予約が無い状態で空欄のまま「確認」した場合は ACSMS-MSG-014-020 が返ること</t>
           </r>
         </is>
       </c>
@@ -19095,7 +18907,7 @@
       <c r="AD63" s="11" t="n"/>
       <c r="AE63" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF63" s="11" t="n"/>
@@ -19139,18 +18951,18 @@
     </row>
     <row r="64" ht="450" customHeight="1">
       <c r="A64" s="44" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B64" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-014-048</t>
+          <t>ACSMS-TC-014-047</t>
         </is>
       </c>
       <c r="C64" s="10" t="n"/>
       <c r="D64" s="11" t="n"/>
       <c r="E64" s="46" t="inlineStr">
         <is>
-          <t>購読中止 — 最終確認ダイアログ（はい／いいえ）</t>
+          <t>購読中止 — 解約確定後は変更・取消できない</t>
         </is>
       </c>
       <c r="F64" s="10" t="n"/>
@@ -19160,7 +18972,7 @@
       <c r="J64" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN
-・事前データ：紙版購読者（`dokusya_id=1022, dokusya_shubetsu=1`／解約予約なし）、電子版購読者（`dokusya_id=1020, dokusya_shubetsu=2, seikyu_kaishi_month='202604'`／2030/07 の解約予約あり）</t>
+・事前データ：電子版購読者（`dokusya_id=1021, dokusya_shubetsu=2`）の解約が到来日バッチで確定済（`kaiyaku_flg=true` の実解約行あり・`tetsuzuki_shurui=0`）</t>
         </is>
       </c>
       <c r="K64" s="10" t="n"/>
@@ -19185,7 +18997,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">紙版（1022）の「購読中止」ポップアップで購読中止日に `2030/09/15` を選び「確認」をクリックする
+            <t xml:space="preserve">検索結果で該当行の「購読中止」リンクの状態を確認する
 </t>
           </r>
           <r>
@@ -19202,7 +19014,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">確認ダイアログで「いいえ」をクリックする
+            <t xml:space="preserve">DevTools で POST `/api/v1/dokusya/1021/stop`（body: `{"dokusya_chushi_date": "2030-09-30"}`）を直接呼び出す
 </t>
           </r>
           <r>
@@ -19219,7 +19031,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">再度「確認」をクリックし、確認ダイアログで「はい」をクリックする
+            <t xml:space="preserve">DevTools で POST `/api/v1/dokusya/1021/stop`（body: `{"dokusya_chushi_date": ""}`）を直接呼び出す
 </t>
           </r>
           <r>
@@ -19236,41 +19048,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">電子版（1020）の「購読中止」ポップアップで終了月を `2030/09` に変更し「確認」をクリックする
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ5：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">電子版（1020）の「購読中止」ポップアップで終了月をクリアして「確認」をクリックする
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ6：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>電子版（1020）の「購読中止」ポップアップで予約中と同じ終了月のまま「確認」をクリックする</t>
+            <t>DB 確認: `SELECT COUNT(*) FROM t_dokusya_rireki WHERE dokusya_id = 1021`</t>
           </r>
         </is>
       </c>
@@ -19296,7 +19074,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">確認ダイアログ「購読中止確認」が表示されること。本文が ACSMS-MSG-014-021 `2030/09/15で購読を中止します。よろしいですか？`、ボタンが「はい」（赤）／「いいえ」であること
+            <t xml:space="preserve">「購読中止」リンクが非活性であること（手続種類=0:解約のため）
 </t>
           </r>
           <r>
@@ -19313,7 +19091,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">APIが呼ばれないこと。購読中止ポップアップが再表示され、選択した `2030/09/15` が保持されていること（確認ダイアログの表示中はポップアップが隠れていること）
+            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: VALIDATION_ERROR`、`errors[0].message` が ACSMS-MSG-014-015 `解約が確定済みのため変更できません。再購読は購読者編集画面から行ってください。`）
 </t>
           </r>
           <r>
@@ -19330,7 +19108,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">APIが呼ばれ、ACSMS-MSG-014-018 が表示されてポップアップが閉じること
+            <t xml:space="preserve">ステップ2と同じ400が返却されること
 </t>
           </r>
           <r>
@@ -19347,41 +19125,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">本文が ACSMS-MSG-014-022 `購読中止日を2030/09の月末（2030/09/30）に変更します。よろしいですか？` であること（電子版は選択月と実際に止まる日の両方が示されること）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ5：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">本文が ACSMS-MSG-014-023 `購読中止の予約を取り消します。よろしいですか？` であること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ6：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">確認ダイアログが表示されないこと。ACSMS-MSG-014-017 `変更がありません。` がポップアップ内に表示され、APIも呼ばれないこと
+            <t xml:space="preserve">履歴の件数が呼び出し前後で変化していないこと（行が追加・取消されていないこと）
 </t>
           </r>
           <r>
@@ -19398,31 +19142,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・確認ダイアログは入力チェック（選択範囲・無変更）を通過した後にのみ表示する。「はい」を押した後にフォームエラーで弾かれないこと
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・確認ダイアログ表示中は購読中止ポップアップを非表示にする。「いいえ」「✕」「ESC」「マスククリック」いずれでも選択内容を保ったまま再表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・APIがエラーを返した場合も購読中止ポップアップが再表示され、エラー内容が表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・ボタンラベルは プロジェクト共通の はい／いいえ（破壊的意図は赤ボタンで示す・`.claude/rules/vue.md §Modal Confirmation`）</t>
+            <t xml:space="preserve">・確定済み判定は解約予約行ではなく `kaiyaku_flg=true` を持つ実解約行の有無で行う（API設計書「処理手順 4.4」準拠）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・復帰は購読者編集画面（SCR-011）の再購読で行う
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・フロントエンド側でリンクが非活性となるが、バックエンド側でも直接呼び出しを拒否すること（観点 VP-C-05）</t>
           </r>
         </is>
       </c>
@@ -19434,7 +19170,7 @@
       <c r="AD64" s="11" t="n"/>
       <c r="AE64" s="45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AF64" s="11" t="n"/>
@@ -19476,11 +19212,1154 @@
       <c r="BP64" s="10" t="n"/>
       <c r="BQ64" s="11" t="n"/>
     </row>
+    <row r="65" ht="450" customHeight="1">
+      <c r="A65" s="44" t="n">
+        <v>48</v>
+      </c>
+      <c r="B65" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-014-048</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="46" t="inlineStr">
+        <is>
+          <t>購読中止 — 最終確認ダイアログ（はい／いいえ）</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="11" t="n"/>
+      <c r="J65" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・事前データ：紙版購読者（`dokusya_id=1022, dokusya_shubetsu=1`／解約予約なし）、電子版購読者（`dokusya_id=1020, dokusya_shubetsu=2, seikyu_kaishi_month='202604'`／2030/07 の解約予約あり）</t>
+        </is>
+      </c>
+      <c r="K65" s="10" t="n"/>
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="10" t="n"/>
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="11" t="n"/>
+      <c r="Q65" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">紙版（1022）の「購読中止」ポップアップで購読中止日に `2030/09/15` を選び「確認」をクリックする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">確認ダイアログで「いいえ」をクリックする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">再度「確認」をクリックし、確認ダイアログで「はい」をクリックする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">電子版（1020）の「購読中止」ポップアップで終了月を `2030/09` に変更し「確認」をクリックする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">電子版（1020）の「購読中止」ポップアップで終了月をクリアして「確認」をクリックする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>電子版（1020）の「購読中止」ポップアップで予約中と同じ終了月のまま「確認」をクリックする</t>
+          </r>
+        </is>
+      </c>
+      <c r="R65" s="10" t="n"/>
+      <c r="S65" s="10" t="n"/>
+      <c r="T65" s="10" t="n"/>
+      <c r="U65" s="10" t="n"/>
+      <c r="V65" s="10" t="n"/>
+      <c r="W65" s="11" t="n"/>
+      <c r="X65" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">確認ダイアログ「購読中止確認」が表示されること。本文が ACSMS-MSG-014-021 `2030/09/15で購読を中止します。よろしいですか？`、ボタンが「はい」（赤）／「いいえ」であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">APIが呼ばれないこと。購読中止ポップアップが再表示され、選択した `2030/09/15` が保持されていること（確認ダイアログの表示中はポップアップが隠れていること）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">APIが呼ばれ、ACSMS-MSG-014-018 が表示されてポップアップが閉じること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">本文が ACSMS-MSG-014-022 `購読中止日を2030/09の月末（2030/09/30）に変更します。よろしいですか？` であること（電子版は選択月と実際に止まる日の両方が示されること）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">本文が ACSMS-MSG-014-023 `購読中止の予約を取り消します。よろしいですか？` であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">確認ダイアログが表示されないこと。ACSMS-MSG-014-017 `変更がありません。` がポップアップ内に表示され、APIも呼ばれないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・確認ダイアログは入力チェック（選択範囲・無変更）を通過した後にのみ表示する。「はい」を押した後にフォームエラーで弾かれないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・確認ダイアログ表示中は購読中止ポップアップを非表示にする。「いいえ」「✕」「ESC」「マスククリック」いずれでも選択内容を保ったまま再表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・APIがエラーを返した場合も購読中止ポップアップが再表示され、エラー内容が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・ボタンラベルは プロジェクト共通の はい／いいえ（破壊的意図は赤ボタンで示す・`.claude/rules/vue.md §Modal Confirmation`）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y65" s="10" t="n"/>
+      <c r="Z65" s="10" t="n"/>
+      <c r="AA65" s="10" t="n"/>
+      <c r="AB65" s="10" t="n"/>
+      <c r="AC65" s="10" t="n"/>
+      <c r="AD65" s="11" t="n"/>
+      <c r="AE65" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF65" s="11" t="n"/>
+      <c r="AG65" s="45" t="inlineStr"/>
+      <c r="AH65" s="10" t="n"/>
+      <c r="AI65" s="11" t="n"/>
+      <c r="AJ65" s="45" t="inlineStr"/>
+      <c r="AK65" s="10" t="n"/>
+      <c r="AL65" s="11" t="n"/>
+      <c r="AM65" s="45" t="inlineStr"/>
+      <c r="AN65" s="10" t="n"/>
+      <c r="AO65" s="11" t="n"/>
+      <c r="AP65" s="45" t="inlineStr"/>
+      <c r="AQ65" s="10" t="n"/>
+      <c r="AR65" s="11" t="n"/>
+      <c r="AS65" s="45" t="inlineStr"/>
+      <c r="AT65" s="10" t="n"/>
+      <c r="AU65" s="11" t="n"/>
+      <c r="AV65" s="45" t="inlineStr"/>
+      <c r="AW65" s="10" t="n"/>
+      <c r="AX65" s="11" t="n"/>
+      <c r="AY65" s="45" t="inlineStr"/>
+      <c r="AZ65" s="10" t="n"/>
+      <c r="BA65" s="11" t="n"/>
+      <c r="BB65" s="45" t="inlineStr"/>
+      <c r="BC65" s="10" t="n"/>
+      <c r="BD65" s="11" t="n"/>
+      <c r="BE65" s="45" t="inlineStr"/>
+      <c r="BF65" s="10" t="n"/>
+      <c r="BG65" s="11" t="n"/>
+      <c r="BH65" s="45" t="inlineStr"/>
+      <c r="BI65" s="10" t="n"/>
+      <c r="BJ65" s="11" t="n"/>
+      <c r="BK65" s="46" t="inlineStr"/>
+      <c r="BL65" s="10" t="n"/>
+      <c r="BM65" s="10" t="n"/>
+      <c r="BN65" s="10" t="n"/>
+      <c r="BO65" s="10" t="n"/>
+      <c r="BP65" s="10" t="n"/>
+      <c r="BQ65" s="11" t="n"/>
+    </row>
+    <row r="66" ht="450" customHeight="1">
+      <c r="A66" s="44" t="n">
+        <v>49</v>
+      </c>
+      <c r="B66" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-014-049</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="n"/>
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="46" t="inlineStr">
+        <is>
+          <t>検索結果 — 「全 N 件」の横に購読部数合計「全 M 部」を表示する（#56240）</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="11" t="n"/>
+      <c r="J66" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属）
+・自JAに購読者が 25 件以上存在し、`dokusya_busu` の合計が 1ページ分の合計と異なること（例：25件・合計 40 部、1ページ目20件の合計は 32 部）
+・そのうち複数の履歴行を持つ購読者が含まれること（適用日絞り込み時の重複検証用）</t>
+        </is>
+      </c>
+      <c r="K66" s="10" t="n"/>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="11" t="n"/>
+      <c r="Q66" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">検索条件を指定せずに検索し、ページネーション部分の表示を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">API レスポンスの `meta` を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">GET /api/v1/dokusya?page=1&amp;per_page=20
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2ページ目に切り替え、「全 M 部」の値が変化しないことを確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">検索条件（例：管理支店）を指定して絞り込み、「全 N 件」「全 M 部」の値を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">**適用日**を指定して検索し（`t_dokusya_rireki` を INNER JOIN する条件）、部数合計をDBの実値と突き合わせる
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT COALESCE(SUM(t.dokusya_busu), 0) FROM (
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT DISTINCT d.dokusya_id, d.dokusya_busu
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_dokusya d /* 画面と同じ絞り込み条件 */
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">) t;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>検索結果が0件になる条件で検索し、表示を確認</t>
+          </r>
+        </is>
+      </c>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="10" t="n"/>
+      <c r="U66" s="10" t="n"/>
+      <c r="V66" s="10" t="n"/>
+      <c r="W66" s="11" t="n"/>
+      <c r="X66" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ページネーションの「全 N 件」の横に「全 M 部」が併記されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`meta` に `total_busu` が含まれ、値が全件の `dokusya_busu` 合計（例：40）であること。1ページ目に表示されている20件の合計（例：32）**ではない**こと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ページを切り替えても「全 M 部」の値が変わらないこと（ページングの影響を受けない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">絞り込み後の件数・部数がいずれも条件に一致する全件で再計算されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">複数の履歴行を持つ購読者がいても部数が水増しされず、DBの実値と一致すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「全 0 件　全 0 部」と表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・素の `SUM(d.dokusya_busu)` では、適用日絞り込みで `t_dokusya_rireki` を INNER JOIN した際に1購読者が履歴行の数だけ重複して部数が水増しされる。件数側は `COUNT(DISTINCT)` のため影響を受けず、**合計だけがずれる**ため気付きにくい（API設計書 §4.4.1）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・ステップ5はこの不一致を検出するための回帰確認。履歴行が1件しかない購読者だけでは検出できないため、複数履歴を持つ購読者を必ず含めること</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y66" s="10" t="n"/>
+      <c r="Z66" s="10" t="n"/>
+      <c r="AA66" s="10" t="n"/>
+      <c r="AB66" s="10" t="n"/>
+      <c r="AC66" s="10" t="n"/>
+      <c r="AD66" s="11" t="n"/>
+      <c r="AE66" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF66" s="11" t="n"/>
+      <c r="AG66" s="45" t="inlineStr"/>
+      <c r="AH66" s="10" t="n"/>
+      <c r="AI66" s="11" t="n"/>
+      <c r="AJ66" s="45" t="inlineStr"/>
+      <c r="AK66" s="10" t="n"/>
+      <c r="AL66" s="11" t="n"/>
+      <c r="AM66" s="45" t="inlineStr"/>
+      <c r="AN66" s="10" t="n"/>
+      <c r="AO66" s="11" t="n"/>
+      <c r="AP66" s="45" t="inlineStr"/>
+      <c r="AQ66" s="10" t="n"/>
+      <c r="AR66" s="11" t="n"/>
+      <c r="AS66" s="45" t="inlineStr"/>
+      <c r="AT66" s="10" t="n"/>
+      <c r="AU66" s="11" t="n"/>
+      <c r="AV66" s="45" t="inlineStr"/>
+      <c r="AW66" s="10" t="n"/>
+      <c r="AX66" s="11" t="n"/>
+      <c r="AY66" s="45" t="inlineStr"/>
+      <c r="AZ66" s="10" t="n"/>
+      <c r="BA66" s="11" t="n"/>
+      <c r="BB66" s="45" t="inlineStr"/>
+      <c r="BC66" s="10" t="n"/>
+      <c r="BD66" s="11" t="n"/>
+      <c r="BE66" s="45" t="inlineStr"/>
+      <c r="BF66" s="10" t="n"/>
+      <c r="BG66" s="11" t="n"/>
+      <c r="BH66" s="45" t="inlineStr"/>
+      <c r="BI66" s="10" t="n"/>
+      <c r="BJ66" s="11" t="n"/>
+      <c r="BK66" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL66" s="10" t="n"/>
+      <c r="BM66" s="10" t="n"/>
+      <c r="BN66" s="10" t="n"/>
+      <c r="BO66" s="10" t="n"/>
+      <c r="BP66" s="10" t="n"/>
+      <c r="BQ66" s="11" t="n"/>
+    </row>
+    <row r="67" ht="450" customHeight="1">
+      <c r="A67" s="44" t="n">
+        <v>50</v>
+      </c>
+      <c r="B67" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-014-050</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="11" t="n"/>
+      <c r="E67" s="46" t="inlineStr">
+        <is>
+          <t>削除 — 削除できるのは紙版のみ（#56422）</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="11" t="n"/>
+      <c r="J67" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属、`dokusya.delete` 権限あり）
+・自JAに以下の購読者が存在すること
+・(a) 紙版（dokusya_shubetsu=1）
+・(b) 電子版・支払方法=口座引落（クレジットカード決済ではない）
+・(c) 電子版・クレジットカード決済
+・(d) 併読（dokusya_shubetsu=3）</t>
+        </is>
+      </c>
+      <c r="K67" s="10" t="n"/>
+      <c r="L67" s="10" t="n"/>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="10" t="n"/>
+      <c r="O67" s="10" t="n"/>
+      <c r="P67" s="11" t="n"/>
+      <c r="Q67" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">検索結果一覧で (a)〜(d) の「削除」ボタンの活性状態を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">API レスポンスの `is_read_only` を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">GET /api/v1/dokusya
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(b) 電子版・口座引落の購読者に対して削除APIを直接実行
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DELETE /api/v1/dokusya/{dokusya_id}
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(c) 電子版・クレカ、(d) 併読 に対して削除APIを直接実行
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(a) 紙版の購読者に対して削除を実行
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">上記実行後、DBで論理削除状態を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT dokusya_id, dokusya_shubetsu, deleted_at FROM t_dokusya WHERE dokusya_id IN (...);
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>```</t>
+          </r>
+        </is>
+      </c>
+      <c r="R67" s="10" t="n"/>
+      <c r="S67" s="10" t="n"/>
+      <c r="T67" s="10" t="n"/>
+      <c r="U67" s="10" t="n"/>
+      <c r="V67" s="10" t="n"/>
+      <c r="W67" s="11" t="n"/>
+      <c r="X67" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(a) のみ「削除」ボタンが活性であること。(b)(c)(d) は非活性であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(c) クレカ決済者と (d) 併読者は `is_read_only: true` であること。(b) 電子版・口座引落は `is_read_only: false` だが、削除ボタンは `dokusya_shubetsu = 1` の条件で非活性となること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード400（`error_code: VALIDATION_ERROR`）が返却され、`errors` に `{"field": "dokusya_shubetsu", "message": "紙版の購読者のみ削除できます。"}` が含まれること。`is_read_only` は 併読 と 電子版クレカ しか弾かないため、このケースはここで初めて拒否される
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">いずれも削除が拒否されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">削除が成功し、`削除しました。` が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(a) のみ `deleted_at` が設定され、(b)(c)(d) は `deleted_at IS NULL` のままであること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・電子版・併読の会員は電子版読者管理システムが正であり、クラウド版で行を消すと同期で復活するか、相手システムとの整合が崩れる（顧客要件2026-08）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・購読停止（解約予約）は電子版でも可能。削除できないのは**行**であって購読の停止ではない</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y67" s="10" t="n"/>
+      <c r="Z67" s="10" t="n"/>
+      <c r="AA67" s="10" t="n"/>
+      <c r="AB67" s="10" t="n"/>
+      <c r="AC67" s="10" t="n"/>
+      <c r="AD67" s="11" t="n"/>
+      <c r="AE67" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF67" s="11" t="n"/>
+      <c r="AG67" s="45" t="inlineStr"/>
+      <c r="AH67" s="10" t="n"/>
+      <c r="AI67" s="11" t="n"/>
+      <c r="AJ67" s="45" t="inlineStr"/>
+      <c r="AK67" s="10" t="n"/>
+      <c r="AL67" s="11" t="n"/>
+      <c r="AM67" s="45" t="inlineStr"/>
+      <c r="AN67" s="10" t="n"/>
+      <c r="AO67" s="11" t="n"/>
+      <c r="AP67" s="45" t="inlineStr"/>
+      <c r="AQ67" s="10" t="n"/>
+      <c r="AR67" s="11" t="n"/>
+      <c r="AS67" s="45" t="inlineStr"/>
+      <c r="AT67" s="10" t="n"/>
+      <c r="AU67" s="11" t="n"/>
+      <c r="AV67" s="45" t="inlineStr"/>
+      <c r="AW67" s="10" t="n"/>
+      <c r="AX67" s="11" t="n"/>
+      <c r="AY67" s="45" t="inlineStr"/>
+      <c r="AZ67" s="10" t="n"/>
+      <c r="BA67" s="11" t="n"/>
+      <c r="BB67" s="45" t="inlineStr"/>
+      <c r="BC67" s="10" t="n"/>
+      <c r="BD67" s="11" t="n"/>
+      <c r="BE67" s="45" t="inlineStr"/>
+      <c r="BF67" s="10" t="n"/>
+      <c r="BG67" s="11" t="n"/>
+      <c r="BH67" s="45" t="inlineStr"/>
+      <c r="BI67" s="10" t="n"/>
+      <c r="BJ67" s="11" t="n"/>
+      <c r="BK67" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL67" s="10" t="n"/>
+      <c r="BM67" s="10" t="n"/>
+      <c r="BN67" s="10" t="n"/>
+      <c r="BO67" s="10" t="n"/>
+      <c r="BP67" s="10" t="n"/>
+      <c r="BQ67" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="887">
+  <mergeCells count="922">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
-    <mergeCell ref="B60:D60"/>
     <mergeCell ref="Q27:W27"/>
     <mergeCell ref="AS46:AU46"/>
     <mergeCell ref="BK58:BQ58"/>
@@ -19491,12 +20370,11 @@
     <mergeCell ref="AE41:AF41"/>
     <mergeCell ref="AV57:AX57"/>
     <mergeCell ref="B53:D53"/>
-    <mergeCell ref="AP60:AR60"/>
+    <mergeCell ref="AS61:AU61"/>
     <mergeCell ref="E39:I39"/>
     <mergeCell ref="E14:I14"/>
-    <mergeCell ref="AS61:AU61"/>
+    <mergeCell ref="AM64:AO64"/>
     <mergeCell ref="W7:Y7"/>
-    <mergeCell ref="AM64:AO64"/>
     <mergeCell ref="AS48:AU48"/>
     <mergeCell ref="J62:P62"/>
     <mergeCell ref="BK16:BQ16"/>
@@ -19510,6 +20388,7 @@
     <mergeCell ref="Q37:W37"/>
     <mergeCell ref="AJ20:AL20"/>
     <mergeCell ref="AM21:AO21"/>
+    <mergeCell ref="AM65:AO65"/>
     <mergeCell ref="AG24:AI24"/>
     <mergeCell ref="BH39:BJ39"/>
     <mergeCell ref="J57:P57"/>
@@ -19543,6 +20422,7 @@
     <mergeCell ref="AE31:AF31"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="AG45:AI45"/>
+    <mergeCell ref="AS67:AU67"/>
     <mergeCell ref="AY29:BA29"/>
     <mergeCell ref="E20:I20"/>
     <mergeCell ref="AJ33:AL33"/>
@@ -19562,21 +20442,24 @@
     <mergeCell ref="AE64:AF64"/>
     <mergeCell ref="AS62:AU62"/>
     <mergeCell ref="AV63:AX63"/>
+    <mergeCell ref="AP66:AR66"/>
     <mergeCell ref="BH49:BJ49"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AP53:AR53"/>
     <mergeCell ref="X16:AD16"/>
     <mergeCell ref="AP28:AR28"/>
     <mergeCell ref="AE57:AF57"/>
+    <mergeCell ref="BK66:BQ66"/>
     <mergeCell ref="BK53:BQ53"/>
-    <mergeCell ref="BH60:BJ60"/>
+    <mergeCell ref="AS64:AU64"/>
     <mergeCell ref="AC7:AE7"/>
-    <mergeCell ref="AS64:AU64"/>
     <mergeCell ref="BE15:BG15"/>
+    <mergeCell ref="J65:P65"/>
     <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="BE33:BG33"/>
     <mergeCell ref="BB37:BD37"/>
     <mergeCell ref="AG50:AI50"/>
+    <mergeCell ref="AP67:AR67"/>
     <mergeCell ref="BK13:BQ13"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="AY57:BA57"/>
@@ -19589,7 +20472,6 @@
     <mergeCell ref="AM24:AO24"/>
     <mergeCell ref="AG27:AI27"/>
     <mergeCell ref="B23:D23"/>
-    <mergeCell ref="AM60:AO60"/>
     <mergeCell ref="BB38:BD38"/>
     <mergeCell ref="AV14:AX14"/>
     <mergeCell ref="Q61:W61"/>
@@ -19649,7 +20531,9 @@
     <mergeCell ref="BH50:BJ50"/>
     <mergeCell ref="Q36:W36"/>
     <mergeCell ref="BE54:BG54"/>
+    <mergeCell ref="AJ67:AL67"/>
     <mergeCell ref="Q30:W30"/>
+    <mergeCell ref="BK67:BQ67"/>
     <mergeCell ref="AE63:AF63"/>
     <mergeCell ref="W1:AH1"/>
     <mergeCell ref="AC8:AE8"/>
@@ -19663,10 +20547,10 @@
     <mergeCell ref="BB59:BD59"/>
     <mergeCell ref="AM63:AO63"/>
     <mergeCell ref="X27:AD27"/>
+    <mergeCell ref="AG66:AI66"/>
     <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="BE57:BG57"/>
     <mergeCell ref="B24:D24"/>
-    <mergeCell ref="AY60:BA60"/>
     <mergeCell ref="BB61:BD61"/>
     <mergeCell ref="AV15:AX15"/>
     <mergeCell ref="AY16:BA16"/>
@@ -19682,6 +20566,7 @@
     <mergeCell ref="E36:I36"/>
     <mergeCell ref="Q51:W51"/>
     <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AV65:AX65"/>
     <mergeCell ref="BH45:BJ45"/>
     <mergeCell ref="AS20:AU20"/>
     <mergeCell ref="AP24:AR24"/>
@@ -19735,11 +20620,13 @@
     <mergeCell ref="AP37:AR37"/>
     <mergeCell ref="J34:P34"/>
     <mergeCell ref="AY37:BA37"/>
+    <mergeCell ref="BE65:BG65"/>
     <mergeCell ref="J49:P49"/>
     <mergeCell ref="J36:P36"/>
     <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
+    <mergeCell ref="AY66:BA66"/>
     <mergeCell ref="AV21:AX21"/>
     <mergeCell ref="AY53:BA53"/>
     <mergeCell ref="BK24:BQ24"/>
@@ -19755,6 +20642,7 @@
     <mergeCell ref="AP63:AR63"/>
     <mergeCell ref="E42:I42"/>
     <mergeCell ref="AY55:BA55"/>
+    <mergeCell ref="Q65:W65"/>
     <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="E44:I44"/>
@@ -19764,6 +20652,7 @@
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
     <mergeCell ref="BE58:BG58"/>
+    <mergeCell ref="AJ65:AL65"/>
     <mergeCell ref="T8:V8"/>
     <mergeCell ref="AP27:AR27"/>
     <mergeCell ref="AS28:AU28"/>
@@ -19780,7 +20669,6 @@
     <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="BE53:BG53"/>
-    <mergeCell ref="AJ60:AL60"/>
     <mergeCell ref="AM32:AO32"/>
     <mergeCell ref="AG64:AI64"/>
     <mergeCell ref="Q7:S7"/>
@@ -19793,13 +20681,14 @@
     <mergeCell ref="E57:I57"/>
     <mergeCell ref="AV50:AX50"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="Q60:W60"/>
     <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="E32:I32"/>
+    <mergeCell ref="BH66:BJ66"/>
     <mergeCell ref="AS41:AU41"/>
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="AG65:AI65"/>
     <mergeCell ref="AV55:AX55"/>
     <mergeCell ref="E47:I47"/>
     <mergeCell ref="BB39:BD39"/>
@@ -19815,6 +20704,7 @@
     <mergeCell ref="F4:AH4"/>
     <mergeCell ref="X51:AD51"/>
     <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="BH67:BJ67"/>
     <mergeCell ref="BH61:BJ61"/>
     <mergeCell ref="AG17:AI17"/>
     <mergeCell ref="AS36:AU36"/>
@@ -19824,17 +20714,19 @@
     <mergeCell ref="J42:P42"/>
     <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
+    <mergeCell ref="AY67:BA67"/>
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="AG19:AI19"/>
     <mergeCell ref="X36:AD36"/>
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="Q25:W25"/>
     <mergeCell ref="AV37:AX37"/>
-    <mergeCell ref="E60:I60"/>
+    <mergeCell ref="BB65:BD65"/>
+    <mergeCell ref="BE66:BG66"/>
+    <mergeCell ref="X67:AD67"/>
     <mergeCell ref="J37:P37"/>
-    <mergeCell ref="AV60:AX60"/>
+    <mergeCell ref="X61:AD61"/>
     <mergeCell ref="Q33:W33"/>
-    <mergeCell ref="X61:AD61"/>
     <mergeCell ref="BK27:BQ27"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="AE29:AF29"/>
@@ -19847,6 +20739,7 @@
     <mergeCell ref="AM42:AO42"/>
     <mergeCell ref="X62:AD62"/>
     <mergeCell ref="AE37:AF37"/>
+    <mergeCell ref="B66:D66"/>
     <mergeCell ref="BH16:BJ16"/>
     <mergeCell ref="AM29:AO29"/>
     <mergeCell ref="BB19:BD19"/>
@@ -19862,6 +20755,7 @@
     <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
     <mergeCell ref="BB58:BD58"/>
+    <mergeCell ref="B67:D67"/>
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="J47:P47"/>
     <mergeCell ref="AV58:AX58"/>
@@ -19871,7 +20765,6 @@
     <mergeCell ref="AJ28:AL28"/>
     <mergeCell ref="BK17:BQ17"/>
     <mergeCell ref="BK55:BQ55"/>
-    <mergeCell ref="BB60:BD60"/>
     <mergeCell ref="AP30:AR30"/>
     <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="AJ30:AL30"/>
@@ -19892,7 +20785,6 @@
     <mergeCell ref="X57:AD57"/>
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="AP41:AR41"/>
-    <mergeCell ref="J60:P60"/>
     <mergeCell ref="BK41:BQ41"/>
     <mergeCell ref="BB13:BD13"/>
     <mergeCell ref="AM17:AO17"/>
@@ -19908,6 +20800,7 @@
     <mergeCell ref="AM46:AO46"/>
     <mergeCell ref="AG22:AI22"/>
     <mergeCell ref="AJ23:AL23"/>
+    <mergeCell ref="E66:I66"/>
     <mergeCell ref="E53:I53"/>
     <mergeCell ref="AM48:AO48"/>
     <mergeCell ref="Q49:W49"/>
@@ -19918,6 +20811,7 @@
     <mergeCell ref="E55:I55"/>
     <mergeCell ref="AE32:AF32"/>
     <mergeCell ref="AV48:AX48"/>
+    <mergeCell ref="E67:I67"/>
     <mergeCell ref="AY14:BA14"/>
     <mergeCell ref="J51:P51"/>
     <mergeCell ref="F2:Q2"/>
@@ -19949,14 +20843,15 @@
     <mergeCell ref="BK61:BQ61"/>
     <mergeCell ref="AJ44:AL44"/>
     <mergeCell ref="Q54:W54"/>
+    <mergeCell ref="AS65:AU65"/>
     <mergeCell ref="AY27:BA27"/>
     <mergeCell ref="AJ31:AL31"/>
     <mergeCell ref="B62:D62"/>
     <mergeCell ref="Q29:W29"/>
+    <mergeCell ref="AV66:AX66"/>
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="X19:AD19"/>
-    <mergeCell ref="AE60:AF60"/>
     <mergeCell ref="AS58:AU58"/>
     <mergeCell ref="AG34:AI34"/>
     <mergeCell ref="AV59:AX59"/>
@@ -19973,7 +20868,6 @@
     <mergeCell ref="BH37:BJ37"/>
     <mergeCell ref="AE45:AF45"/>
     <mergeCell ref="X58:AD58"/>
-    <mergeCell ref="AS60:AU60"/>
     <mergeCell ref="AV61:AX61"/>
     <mergeCell ref="AP64:AR64"/>
     <mergeCell ref="Z7:AB7"/>
@@ -19981,8 +20875,9 @@
     <mergeCell ref="AP51:AR51"/>
     <mergeCell ref="AG59:AI59"/>
     <mergeCell ref="BK64:BQ64"/>
+    <mergeCell ref="J66:P66"/>
     <mergeCell ref="BK51:BQ51"/>
-    <mergeCell ref="X60:AD60"/>
+    <mergeCell ref="AM67:AO67"/>
     <mergeCell ref="AM61:AO61"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="BB54:BD54"/>
@@ -19993,6 +20888,7 @@
     <mergeCell ref="AE46:AF46"/>
     <mergeCell ref="BH51:BJ51"/>
     <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AP65:AR65"/>
     <mergeCell ref="AM20:AO20"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="B19:D19"/>
@@ -20040,11 +20936,13 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="AG49:AI49"/>
     <mergeCell ref="AE51:AF51"/>
+    <mergeCell ref="AV67:AX67"/>
     <mergeCell ref="BB29:BD29"/>
     <mergeCell ref="BB23:BD23"/>
     <mergeCell ref="E24:I24"/>
     <mergeCell ref="AG36:AI36"/>
     <mergeCell ref="B13:D13"/>
+    <mergeCell ref="AE66:AF66"/>
     <mergeCell ref="Q45:W45"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="BB31:BD31"/>
@@ -20054,7 +20952,11 @@
     <mergeCell ref="BE42:BG42"/>
     <mergeCell ref="Q47:W47"/>
     <mergeCell ref="BH13:BJ13"/>
+    <mergeCell ref="AS66:AU66"/>
     <mergeCell ref="E19:I19"/>
+    <mergeCell ref="BK65:BQ65"/>
+    <mergeCell ref="J67:P67"/>
+    <mergeCell ref="AE67:AF67"/>
     <mergeCell ref="BK21:BQ21"/>
     <mergeCell ref="BB56:BD56"/>
     <mergeCell ref="AE61:AF61"/>
@@ -20098,7 +21000,6 @@
     <mergeCell ref="BH43:BJ43"/>
     <mergeCell ref="BE47:BG47"/>
     <mergeCell ref="AP22:AR22"/>
-    <mergeCell ref="BK60:BQ60"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="BE40:BG40"/>
     <mergeCell ref="AP15:AR15"/>
@@ -20133,7 +21034,6 @@
     <mergeCell ref="X28:AD28"/>
     <mergeCell ref="AS30:AU30"/>
     <mergeCell ref="BB47:BD47"/>
-    <mergeCell ref="AG60:AI60"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="AS42:AU42"/>
     <mergeCell ref="A35:BQ35"/>
@@ -20143,6 +21043,7 @@
     <mergeCell ref="X30:AD30"/>
     <mergeCell ref="BE45:BG45"/>
     <mergeCell ref="AJ58:AL58"/>
+    <mergeCell ref="BH65:BJ65"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BH56:BJ56"/>
@@ -20153,6 +21054,7 @@
     <mergeCell ref="BE59:BG59"/>
     <mergeCell ref="AY62:BA62"/>
     <mergeCell ref="BB63:BD63"/>
+    <mergeCell ref="AJ66:AL66"/>
     <mergeCell ref="BE46:BG46"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
@@ -20162,6 +21064,7 @@
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="AY64:BA64"/>
     <mergeCell ref="AV19:AX19"/>
+    <mergeCell ref="Q66:W66"/>
     <mergeCell ref="AS23:AU23"/>
     <mergeCell ref="E38:I38"/>
     <mergeCell ref="AY51:BA51"/>
@@ -20186,6 +21089,7 @@
     <mergeCell ref="AJ59:AL59"/>
     <mergeCell ref="AP21:AR21"/>
     <mergeCell ref="B54:D54"/>
+    <mergeCell ref="AE65:AF65"/>
     <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="AJ21:AL21"/>
     <mergeCell ref="J27:P27"/>
@@ -20228,6 +21132,7 @@
     <mergeCell ref="AS37:AU37"/>
     <mergeCell ref="AE14:AF14"/>
     <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="BE67:BG67"/>
     <mergeCell ref="J38:P38"/>
     <mergeCell ref="K7:M7"/>
     <mergeCell ref="A3:E3"/>
@@ -20242,10 +21147,13 @@
     <mergeCell ref="J40:P40"/>
     <mergeCell ref="BE62:BG62"/>
     <mergeCell ref="J15:P15"/>
+    <mergeCell ref="AY65:BA65"/>
     <mergeCell ref="AM41:AO41"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="AY21:BA21"/>
     <mergeCell ref="E61:I61"/>
+    <mergeCell ref="BB66:BD66"/>
+    <mergeCell ref="Q67:W67"/>
     <mergeCell ref="BE64:BG64"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
@@ -20255,6 +21163,8 @@
     <mergeCell ref="AY23:BA23"/>
     <mergeCell ref="AS63:AU63"/>
     <mergeCell ref="E41:I41"/>
+    <mergeCell ref="X65:AD65"/>
+    <mergeCell ref="AM66:AO66"/>
     <mergeCell ref="AE27:AF27"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
@@ -20272,6 +21182,7 @@
     <mergeCell ref="BK29:BQ29"/>
     <mergeCell ref="AS40:AU40"/>
     <mergeCell ref="X50:AD50"/>
+    <mergeCell ref="A60:BQ60"/>
     <mergeCell ref="AS27:AU27"/>
     <mergeCell ref="AP31:AR31"/>
     <mergeCell ref="BH14:BJ14"/>
@@ -20285,12 +21196,14 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="Q16:W16"/>
     <mergeCell ref="AV40:AX40"/>
+    <mergeCell ref="B65:D65"/>
     <mergeCell ref="AJ64:AL64"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="J28:P28"/>
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="BK49:BQ49"/>
+    <mergeCell ref="AG67:AI67"/>
     <mergeCell ref="B63:D63"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AE38:AF38"/>
@@ -20323,6 +21236,7 @@
     <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="J41:P41"/>
     <mergeCell ref="Q44:W44"/>
+    <mergeCell ref="BB67:BD67"/>
     <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="AJ19:AL19"/>
     <mergeCell ref="E62:I62"/>
@@ -20340,10 +21254,12 @@
     <mergeCell ref="BB21:BD21"/>
     <mergeCell ref="N6:P6"/>
     <mergeCell ref="AM25:AO25"/>
+    <mergeCell ref="E65:I65"/>
     <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
     <mergeCell ref="BH64:BJ64"/>
+    <mergeCell ref="X66:AD66"/>
     <mergeCell ref="BE19:BG19"/>
     <mergeCell ref="BK32:BQ32"/>
     <mergeCell ref="AM33:AO33"/>
@@ -20364,16 +21280,15 @@
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="AV56:AX56"/>
     <mergeCell ref="B58:D58"/>
-    <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE17 AE19:AE25 AE27:AE34 AE36:AE51 AE53:AE64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE17 AE19:AE25 AE27:AE34 AE36:AE51 AE53:AE59 AE61:AE67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG17 AG19:AG25 AG27:AG34 AG36:AG51 AG53:AG64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG17 AG19:AG25 AG27:AG34 AG36:AG51 AG53:AG59 AG61:AG67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV17 AV19:AV25 AV27:AV34 AV36:AV51 AV53:AV64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV17 AV19:AV25 AV27:AV34 AV36:AV51 AV53:AV59 AV61:AV67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
